--- a/ContabilidadeFinanceira/Treinos/Ex5_MarGrosso.xlsx
+++ b/ContabilidadeFinanceira/Treinos/Ex5_MarGrosso.xlsx
@@ -44,14 +44,14 @@
       <b val="1"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="8"/>
+    </font>
+    <font>
       <b val="1"/>
       <i val="1"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00808080"/>
-      <sz val="8"/>
     </font>
     <font>
       <b val="1"/>
@@ -120,28 +120,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -522,17 +524,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="3" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -545,14 +550,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Uma linha por movimento. Se a transação mexe em duas contas do mesmo lado (ex: sai caixa, entra estoque), usa as duas linhas.</t>
+          <t>Uma linha por movimento: escreve a conta e o valor, com sinal. Transação que mexe em três contas do mesmo lado usa as três linhas. A coluna Check acusa se aquela transação fechou.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Transação</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -565,575 +570,714 @@
           <t>ATIVO</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>PASSIVO</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>PATRIMÔNIO LÍQUIDO</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="4" t="n">
+    <row r="5">
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>conta</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>conta</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>conta</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Vendas do ano de 520, sendo 380 à vista e 140 a prazo; o custo das mercadorias vendidas foi de 300</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="8">
-        <f>IF(COUNT(C5:C6,E5:E6,G5:G6)=0,"",IF(SUM(C5:C6)-SUM(E5:E6)-SUM(G5:G6)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="I6" s="8" t="n"/>
+      <c r="J6" s="9" t="n"/>
+      <c r="K6" s="6">
+        <f>IF(COUNT(D6:D8,G6:G8,J6:J8)=0,"",IF(SUM(D6:D8)-SUM(G6:G8)-SUM(J6:J8)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="9" t="n"/>
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="4" t="n">
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="9" t="n"/>
+    </row>
+    <row r="8">
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="9" t="n"/>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="9" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Compras de estoque no ano: 330, integralmente a prazo</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="9" t="n"/>
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="8">
-        <f>IF(COUNT(C7:C8,E7:E8,G7:G8)=0,"",IF(SUM(C7:C8)-SUM(E7:E8)-SUM(G7:G8)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="I9" s="8" t="n"/>
+      <c r="J9" s="9" t="n"/>
+      <c r="K9" s="6">
+        <f>IF(COUNT(D9:D10,G9:G10,J9:J10)=0,"",IF(SUM(D9:D10)-SUM(G9:G10)-SUM(J9:J10)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="4" t="n">
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="9" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Recebimento de 95 de clientes, referente a vendas de anos anteriores</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="8">
-        <f>IF(COUNT(C9:C10,E9:E10,G9:G10)=0,"",IF(SUM(C9:C10)-SUM(E9:E10)-SUM(G9:G10)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="I11" s="8" t="n"/>
+      <c r="J11" s="9" t="n"/>
+      <c r="K11" s="6">
+        <f>IF(COUNT(D11:D12,G11:G12,J11:J12)=0,"",IF(SUM(D11:D12)-SUM(G11:G12)-SUM(J11:J12)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="9" t="n"/>
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G10" s="6" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="4" t="n">
+      <c r="I12" s="8" t="n"/>
+      <c r="J12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Pagamento de 310 a fornecedores</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="8">
-        <f>IF(COUNT(C11:C12,E11:E12,G11:G12)=0,"",IF(SUM(C11:C12)-SUM(E11:E12)-SUM(G11:G12)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="9" t="n"/>
+      <c r="K13" s="6">
+        <f>IF(COUNT(D13:D14,G13:G14,J13:J14)=0,"",IF(SUM(D13:D14)-SUM(G13:G14)-SUM(J13:J14)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="9" t="n"/>
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="4" t="n">
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Cliente corporativo adianta 25 por uma encomenda que só será entregue no ano seguinte</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F15" s="8" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="8">
-        <f>IF(COUNT(C13:C14,E13:E14,G13:G14)=0,"",IF(SUM(C13:C14)-SUM(E13:E14)-SUM(G13:G14)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="I15" s="8" t="n"/>
+      <c r="J15" s="9" t="n"/>
+      <c r="K15" s="6">
+        <f>IF(COUNT(D15:D16,G15:G16,J15:J16)=0,"",IF(SUM(D15:D16)-SUM(G15:G16)-SUM(J15:J16)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G14" s="6" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="4" t="n">
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Despesas de vendas e administrativas de 90, pagas à vista</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="8">
-        <f>IF(COUNT(C15:C16,E15:E16,G15:G16)=0,"",IF(SUM(C15:C16)-SUM(E15:E16)-SUM(G15:G16)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="I17" s="8" t="n"/>
+      <c r="J17" s="9" t="n"/>
+      <c r="K17" s="6">
+        <f>IF(COUNT(D17:D18,G17:G18,J17:J18)=0,"",IF(SUM(D17:D18)-SUM(G17:G18)-SUM(J17:J18)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="9" t="n"/>
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G16" s="6" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="4" t="n">
+      <c r="I18" s="8" t="n"/>
+      <c r="J18" s="9" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Depreciação do imobilizado no ano: 30</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="9" t="n"/>
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="8">
-        <f>IF(COUNT(C17:C18,E17:E18,G17:G18)=0,"",IF(SUM(C17:C18)-SUM(E17:E18)-SUM(G17:G18)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="9" t="n"/>
+      <c r="K19" s="6">
+        <f>IF(COUNT(D19:D20,G19:G20,J19:J20)=0,"",IF(SUM(D19:D20)-SUM(G19:G20)-SUM(J19:J20)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="9" t="n"/>
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G18" s="6" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="4" t="n">
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Captação de novo empréstimo bancário de 80</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="9" t="n"/>
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="8">
-        <f>IF(COUNT(C19:C20,E19:E20,G19:G20)=0,"",IF(SUM(C19:C20)-SUM(E19:E20)-SUM(G19:G20)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="I21" s="8" t="n"/>
+      <c r="J21" s="9" t="n"/>
+      <c r="K21" s="6">
+        <f>IF(COUNT(D21:D22,G21:G22,J21:J22)=0,"",IF(SUM(D21:D22)-SUM(G21:G22)-SUM(J21:J22)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="9" t="n"/>
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G20" s="6" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="4" t="n">
+      <c r="I22" s="8" t="n"/>
+      <c r="J22" s="9" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Amortização de 50 do principal da dívida e pagamento de 10 de juros do período</t>
         </is>
       </c>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F23" s="8" t="n"/>
+      <c r="G23" s="9" t="n"/>
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="8">
-        <f>IF(COUNT(C21:C22,E21:E22,G21:G22)=0,"",IF(SUM(C21:C22)-SUM(E21:E22)-SUM(G21:G22)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="I23" s="8" t="n"/>
+      <c r="J23" s="9" t="n"/>
+      <c r="K23" s="6">
+        <f>IF(COUNT(D23:D24,G23:G24,J23:J24)=0,"",IF(SUM(D23:D24)-SUM(G23:G24)-SUM(J23:J24)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="9" t="n"/>
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G22" s="6" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="4" t="n">
+      <c r="I24" s="8" t="n"/>
+      <c r="J24" s="9" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>Compra de um novo forno por 120, pagando 45 à vista e 75 em financiamento de longo prazo</t>
         </is>
       </c>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="F25" s="8" t="n"/>
+      <c r="G25" s="9" t="n"/>
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="8">
-        <f>IF(COUNT(C23:C24,E23:E24,G23:G24)=0,"",IF(SUM(C23:C24)-SUM(E23:E24)-SUM(G23:G24)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="I25" s="8" t="n"/>
+      <c r="J25" s="9" t="n"/>
+      <c r="K25" s="6">
+        <f>IF(COUNT(D25:D26,G25:G26,J25:J26)=0,"",IF(SUM(D25:D26)-SUM(G25:G26)-SUM(J25:J26)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="9" t="n"/>
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G24" s="6" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="4" t="n">
+      <c r="I26" s="8" t="n"/>
+      <c r="J26" s="9" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>IR e CSLL do ano: 27, sendo 20 pagos à vista e 7 a recolher no ano seguinte</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F27" s="8" t="n"/>
+      <c r="G27" s="9" t="n"/>
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="8">
-        <f>IF(COUNT(C25:C26,E25:E26,G25:G26)=0,"",IF(SUM(C25:C26)-SUM(E25:E26)-SUM(G25:G26)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="I27" s="8" t="n"/>
+      <c r="J27" s="9" t="n"/>
+      <c r="K27" s="6">
+        <f>IF(COUNT(D27:D28,G27:G28,J27:J28)=0,"",IF(SUM(D27:D28)-SUM(G27:G28)-SUM(J27:J28)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="9" t="n"/>
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G26" s="6" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="4" t="n">
+      <c r="I28" s="8" t="n"/>
+      <c r="J28" s="9" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>Dividendos de 25 declarados e pagos em dinheiro</t>
         </is>
       </c>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F29" s="8" t="n"/>
+      <c r="G29" s="9" t="n"/>
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="8">
-        <f>IF(COUNT(C27:C28,E27:E28,G27:G28)=0,"",IF(SUM(C27:C28)-SUM(E27:E28)-SUM(G27:G28)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="I29" s="8" t="n"/>
+      <c r="J29" s="9" t="n"/>
+      <c r="K29" s="6">
+        <f>IF(COUNT(D29:D30,G29:G30,J29:J30)=0,"",IF(SUM(D29:D30)-SUM(G29:G30)-SUM(J29:J30)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E28" s="6" t="n"/>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F30" s="8" t="n"/>
+      <c r="G30" s="9" t="n"/>
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G28" s="6" t="n"/>
+      <c r="I30" s="8" t="n"/>
+      <c r="J30" s="9" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="39">
+    <mergeCell ref="F4:G4"/>
     <mergeCell ref="B27:B28"/>
-    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="K21:K22"/>
     <mergeCell ref="B17:B18"/>
-    <mergeCell ref="A7:A8"/>
     <mergeCell ref="B11:B12"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C4:D4"/>
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="A27:A28"/>
-    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="K27:K28"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="A25:A26"/>
-    <mergeCell ref="H7:H8"/>
     <mergeCell ref="B19:B20"/>
-    <mergeCell ref="H19:H20"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A5:A6"/>
     <mergeCell ref="B9:B10"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="H27:H28"/>
     <mergeCell ref="A17:A18"/>
+    <mergeCell ref="K17:K18"/>
     <mergeCell ref="A13:A14"/>
+    <mergeCell ref="K23:K24"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="K13:K14"/>
     <mergeCell ref="A23:A24"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="A6:A8"/>
     <mergeCell ref="A19:A20"/>
-    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="K19:K20"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K9:K10"/>
     <mergeCell ref="A9:A10"/>
+    <mergeCell ref="K25:K26"/>
     <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B7:B8"/>
     <mergeCell ref="B25:B26"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="K29:K30"/>
     <mergeCell ref="B21:B22"/>
     <mergeCell ref="A11:A12"/>
   </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Caixa,Contas a Receber,Estoques,Imobilizado,(-) Depreciação Acumulada"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Fornecedores,Adiantamentos de Clientes,IR a Pagar,Empréstimos,Financiamento a Pagar (LP)"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Capital Social,Lucros Acumulados"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1173,81 +1317,81 @@
           <t>Cervejaria Mar Grosso S.A.  |  Ano 2  |  valores em R$ mil</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Transações, por Número e Descrição</t>
         </is>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>Vendas do ano de 520, sendo 380 à vista e 140 a prazo; o cus</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>Compras de estoque no ano: 330, integralmente a prazo</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>Recebimento de 95 de clientes, referente a vendas de anos an</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>Pagamento de 310 a fornecedores</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>Cliente corporativo adianta 25 por uma encomenda que só será</t>
         </is>
       </c>
-      <c r="I2" s="10" t="inlineStr">
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>Despesas de vendas e administrativas de 90, pagas à vista</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr">
+      <c r="J2" s="12" t="inlineStr">
         <is>
           <t>Depreciação do imobilizado no ano: 30</t>
         </is>
       </c>
-      <c r="K2" s="10" t="inlineStr">
+      <c r="K2" s="12" t="inlineStr">
         <is>
           <t>Captação de novo empréstimo bancário de 80</t>
         </is>
       </c>
-      <c r="L2" s="10" t="inlineStr">
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>Amortização de 50 do principal da dívida e pagamento de 10 d</t>
         </is>
       </c>
-      <c r="M2" s="10" t="inlineStr">
+      <c r="M2" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Compra de um novo forno por 120, pagando 45 à vista e 75 em </t>
         </is>
       </c>
-      <c r="N2" s="10" t="inlineStr">
+      <c r="N2" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">IR e CSLL do ano: 27, sendo 20 pagos à vista e 7 a recolher </t>
         </is>
       </c>
-      <c r="O2" s="10" t="inlineStr">
+      <c r="O2" s="12" t="inlineStr">
         <is>
           <t>Dividendos de 25 declarados e pagos em dinheiro</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Balanço Patrimonial</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Balanço Inicial</t>
         </is>
@@ -1288,21 +1432,21 @@
       <c r="O3" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="P3" s="11" t="inlineStr">
+      <c r="P3" s="13" t="inlineStr">
         <is>
           <t>Balanço Final</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>ATIVO</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>Ativo Circulante</t>
         </is>
@@ -1314,26 +1458,26 @@
           <t>Caixa</t>
         </is>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="16" t="n">
         <v>40</v>
       </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="6" t="n"/>
-      <c r="M6" s="6" t="n"/>
-      <c r="N6" s="6" t="n"/>
-      <c r="O6" s="6" t="n"/>
-      <c r="P6" s="15">
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
+      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="9" t="n"/>
+      <c r="I6" s="9" t="n"/>
+      <c r="J6" s="9" t="n"/>
+      <c r="K6" s="9" t="n"/>
+      <c r="L6" s="9" t="n"/>
+      <c r="M6" s="9" t="n"/>
+      <c r="N6" s="9" t="n"/>
+      <c r="O6" s="9" t="n"/>
+      <c r="P6" s="17">
         <f>C6+SUM(D6:O6)</f>
         <v/>
       </c>
-      <c r="R6" s="16">
+      <c r="R6" s="18">
         <f>IF(COUNT(D6:O6)=0,"",IF(ABS(P6-Gabarito!P6)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
@@ -1344,26 +1488,26 @@
           <t>Contas a Receber</t>
         </is>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="16" t="n">
         <v>60</v>
       </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-      <c r="M7" s="6" t="n"/>
-      <c r="N7" s="6" t="n"/>
-      <c r="O7" s="6" t="n"/>
-      <c r="P7" s="15">
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="9" t="n"/>
+      <c r="G7" s="9" t="n"/>
+      <c r="H7" s="9" t="n"/>
+      <c r="I7" s="9" t="n"/>
+      <c r="J7" s="9" t="n"/>
+      <c r="K7" s="9" t="n"/>
+      <c r="L7" s="9" t="n"/>
+      <c r="M7" s="9" t="n"/>
+      <c r="N7" s="9" t="n"/>
+      <c r="O7" s="9" t="n"/>
+      <c r="P7" s="17">
         <f>C7+SUM(D7:O7)</f>
         <v/>
       </c>
-      <c r="R7" s="16">
+      <c r="R7" s="18">
         <f>IF(COUNT(D7:O7)=0,"",IF(ABS(P7-Gabarito!P7)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
@@ -1374,32 +1518,32 @@
           <t>Estoques</t>
         </is>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="16" t="n">
         <v>90</v>
       </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
-      <c r="M8" s="6" t="n"/>
-      <c r="N8" s="6" t="n"/>
-      <c r="O8" s="6" t="n"/>
-      <c r="P8" s="15">
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="9" t="n"/>
+      <c r="H8" s="9" t="n"/>
+      <c r="I8" s="9" t="n"/>
+      <c r="J8" s="9" t="n"/>
+      <c r="K8" s="9" t="n"/>
+      <c r="L8" s="9" t="n"/>
+      <c r="M8" s="9" t="n"/>
+      <c r="N8" s="9" t="n"/>
+      <c r="O8" s="9" t="n"/>
+      <c r="P8" s="17">
         <f>C8+SUM(D8:O8)</f>
         <v/>
       </c>
-      <c r="R8" s="16">
+      <c r="R8" s="18">
         <f>IF(COUNT(D8:O8)=0,"",IF(ABS(P8-Gabarito!P8)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Ativo Não Circulante</t>
         </is>
@@ -1411,26 +1555,26 @@
           <t>Imobilizado</t>
         </is>
       </c>
-      <c r="C10" s="14" t="n">
+      <c r="C10" s="16" t="n">
         <v>300</v>
       </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="6" t="n"/>
-      <c r="M10" s="6" t="n"/>
-      <c r="N10" s="6" t="n"/>
-      <c r="O10" s="6" t="n"/>
-      <c r="P10" s="15">
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="9" t="n"/>
+      <c r="I10" s="9" t="n"/>
+      <c r="J10" s="9" t="n"/>
+      <c r="K10" s="9" t="n"/>
+      <c r="L10" s="9" t="n"/>
+      <c r="M10" s="9" t="n"/>
+      <c r="N10" s="9" t="n"/>
+      <c r="O10" s="9" t="n"/>
+      <c r="P10" s="17">
         <f>C10+SUM(D10:O10)</f>
         <v/>
       </c>
-      <c r="R10" s="16">
+      <c r="R10" s="18">
         <f>IF(COUNT(D10:O10)=0,"",IF(ABS(P10-Gabarito!P10)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
@@ -1441,102 +1585,102 @@
           <t>(-) Depreciação Acumulada</t>
         </is>
       </c>
-      <c r="C11" s="14" t="n">
+      <c r="C11" s="16" t="n">
         <v>-60</v>
       </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="6" t="n"/>
-      <c r="M11" s="6" t="n"/>
-      <c r="N11" s="6" t="n"/>
-      <c r="O11" s="6" t="n"/>
-      <c r="P11" s="15">
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="9" t="n"/>
+      <c r="I11" s="9" t="n"/>
+      <c r="J11" s="9" t="n"/>
+      <c r="K11" s="9" t="n"/>
+      <c r="L11" s="9" t="n"/>
+      <c r="M11" s="9" t="n"/>
+      <c r="N11" s="9" t="n"/>
+      <c r="O11" s="9" t="n"/>
+      <c r="P11" s="17">
         <f>C11+SUM(D11:O11)</f>
         <v/>
       </c>
-      <c r="R11" s="16">
+      <c r="R11" s="18">
         <f>IF(COUNT(D11:O11)=0,"",IF(ABS(P11-Gabarito!P11)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  Total do Ativo</t>
         </is>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="20">
         <f>SUM(C6:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="20">
         <f>SUM(D6:D11)</f>
         <v/>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="20">
         <f>SUM(E6:E11)</f>
         <v/>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="20">
         <f>SUM(F6:F11)</f>
         <v/>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="20">
         <f>SUM(G6:G11)</f>
         <v/>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="20">
         <f>SUM(H6:H11)</f>
         <v/>
       </c>
-      <c r="I12" s="18">
+      <c r="I12" s="20">
         <f>SUM(I6:I11)</f>
         <v/>
       </c>
-      <c r="J12" s="18">
+      <c r="J12" s="20">
         <f>SUM(J6:J11)</f>
         <v/>
       </c>
-      <c r="K12" s="18">
+      <c r="K12" s="20">
         <f>SUM(K6:K11)</f>
         <v/>
       </c>
-      <c r="L12" s="18">
+      <c r="L12" s="20">
         <f>SUM(L6:L11)</f>
         <v/>
       </c>
-      <c r="M12" s="18">
+      <c r="M12" s="20">
         <f>SUM(M6:M11)</f>
         <v/>
       </c>
-      <c r="N12" s="18">
+      <c r="N12" s="20">
         <f>SUM(N6:N11)</f>
         <v/>
       </c>
-      <c r="O12" s="18">
+      <c r="O12" s="20">
         <f>SUM(O6:O11)</f>
         <v/>
       </c>
-      <c r="P12" s="18">
+      <c r="P12" s="20">
         <f>SUM(P6:P11)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>PASSIVO E PATRIM. LÍQUIDO</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>Passivo Circulante:</t>
         </is>
@@ -1548,26 +1692,26 @@
           <t>Fornecedores</t>
         </is>
       </c>
-      <c r="C15" s="14" t="n">
+      <c r="C15" s="16" t="n">
         <v>70</v>
       </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
-      <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="6" t="n"/>
-      <c r="M15" s="6" t="n"/>
-      <c r="N15" s="6" t="n"/>
-      <c r="O15" s="6" t="n"/>
-      <c r="P15" s="15">
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="9" t="n"/>
+      <c r="I15" s="9" t="n"/>
+      <c r="J15" s="9" t="n"/>
+      <c r="K15" s="9" t="n"/>
+      <c r="L15" s="9" t="n"/>
+      <c r="M15" s="9" t="n"/>
+      <c r="N15" s="9" t="n"/>
+      <c r="O15" s="9" t="n"/>
+      <c r="P15" s="17">
         <f>C15+SUM(D15:O15)</f>
         <v/>
       </c>
-      <c r="R15" s="16">
+      <c r="R15" s="18">
         <f>IF(COUNT(D15:O15)=0,"",IF(ABS(P15-Gabarito!P15)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
@@ -1578,24 +1722,24 @@
           <t>Adiantamentos de Clientes</t>
         </is>
       </c>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
-      <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="6" t="n"/>
-      <c r="L16" s="6" t="n"/>
-      <c r="M16" s="6" t="n"/>
-      <c r="N16" s="6" t="n"/>
-      <c r="O16" s="6" t="n"/>
-      <c r="P16" s="15">
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="9" t="n"/>
+      <c r="I16" s="9" t="n"/>
+      <c r="J16" s="9" t="n"/>
+      <c r="K16" s="9" t="n"/>
+      <c r="L16" s="9" t="n"/>
+      <c r="M16" s="9" t="n"/>
+      <c r="N16" s="9" t="n"/>
+      <c r="O16" s="9" t="n"/>
+      <c r="P16" s="17">
         <f>C16+SUM(D16:O16)</f>
         <v/>
       </c>
-      <c r="R16" s="16">
+      <c r="R16" s="18">
         <f>IF(COUNT(D16:O16)=0,"",IF(ABS(P16-Gabarito!P16)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
@@ -1606,24 +1750,24 @@
           <t>IR a Pagar</t>
         </is>
       </c>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
-      <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="6" t="n"/>
-      <c r="L17" s="6" t="n"/>
-      <c r="M17" s="6" t="n"/>
-      <c r="N17" s="6" t="n"/>
-      <c r="O17" s="6" t="n"/>
-      <c r="P17" s="15">
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="9" t="n"/>
+      <c r="I17" s="9" t="n"/>
+      <c r="J17" s="9" t="n"/>
+      <c r="K17" s="9" t="n"/>
+      <c r="L17" s="9" t="n"/>
+      <c r="M17" s="9" t="n"/>
+      <c r="N17" s="9" t="n"/>
+      <c r="O17" s="9" t="n"/>
+      <c r="P17" s="17">
         <f>C17+SUM(D17:O17)</f>
         <v/>
       </c>
-      <c r="R17" s="16">
+      <c r="R17" s="18">
         <f>IF(COUNT(D17:O17)=0,"",IF(ABS(P17-Gabarito!P17)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
@@ -1634,32 +1778,32 @@
           <t>Empréstimos</t>
         </is>
       </c>
-      <c r="C18" s="14" t="n">
+      <c r="C18" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
-      <c r="I18" s="6" t="n"/>
-      <c r="J18" s="6" t="n"/>
-      <c r="K18" s="6" t="n"/>
-      <c r="L18" s="6" t="n"/>
-      <c r="M18" s="6" t="n"/>
-      <c r="N18" s="6" t="n"/>
-      <c r="O18" s="6" t="n"/>
-      <c r="P18" s="15">
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="9" t="n"/>
+      <c r="H18" s="9" t="n"/>
+      <c r="I18" s="9" t="n"/>
+      <c r="J18" s="9" t="n"/>
+      <c r="K18" s="9" t="n"/>
+      <c r="L18" s="9" t="n"/>
+      <c r="M18" s="9" t="n"/>
+      <c r="N18" s="9" t="n"/>
+      <c r="O18" s="9" t="n"/>
+      <c r="P18" s="17">
         <f>C18+SUM(D18:O18)</f>
         <v/>
       </c>
-      <c r="R18" s="16">
+      <c r="R18" s="18">
         <f>IF(COUNT(D18:O18)=0,"",IF(ABS(P18-Gabarito!P18)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>Passivo Não Circulante:</t>
         </is>
@@ -1671,30 +1815,30 @@
           <t>Financiamento a Pagar (LP)</t>
         </is>
       </c>
-      <c r="C20" s="14" t="n"/>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
-      <c r="I20" s="6" t="n"/>
-      <c r="J20" s="6" t="n"/>
-      <c r="K20" s="6" t="n"/>
-      <c r="L20" s="6" t="n"/>
-      <c r="M20" s="6" t="n"/>
-      <c r="N20" s="6" t="n"/>
-      <c r="O20" s="6" t="n"/>
-      <c r="P20" s="15">
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="9" t="n"/>
+      <c r="H20" s="9" t="n"/>
+      <c r="I20" s="9" t="n"/>
+      <c r="J20" s="9" t="n"/>
+      <c r="K20" s="9" t="n"/>
+      <c r="L20" s="9" t="n"/>
+      <c r="M20" s="9" t="n"/>
+      <c r="N20" s="9" t="n"/>
+      <c r="O20" s="9" t="n"/>
+      <c r="P20" s="17">
         <f>C20+SUM(D20:O20)</f>
         <v/>
       </c>
-      <c r="R20" s="16">
+      <c r="R20" s="18">
         <f>IF(COUNT(D20:O20)=0,"",IF(ABS(P20-Gabarito!P20)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>Patrimônio Líquido:</t>
         </is>
@@ -1706,26 +1850,26 @@
           <t>Capital Social</t>
         </is>
       </c>
-      <c r="C22" s="14" t="n">
+      <c r="C22" s="16" t="n">
         <v>200</v>
       </c>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
-      <c r="I22" s="6" t="n"/>
-      <c r="J22" s="6" t="n"/>
-      <c r="K22" s="6" t="n"/>
-      <c r="L22" s="6" t="n"/>
-      <c r="M22" s="6" t="n"/>
-      <c r="N22" s="6" t="n"/>
-      <c r="O22" s="6" t="n"/>
-      <c r="P22" s="15">
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="9" t="n"/>
+      <c r="G22" s="9" t="n"/>
+      <c r="H22" s="9" t="n"/>
+      <c r="I22" s="9" t="n"/>
+      <c r="J22" s="9" t="n"/>
+      <c r="K22" s="9" t="n"/>
+      <c r="L22" s="9" t="n"/>
+      <c r="M22" s="9" t="n"/>
+      <c r="N22" s="9" t="n"/>
+      <c r="O22" s="9" t="n"/>
+      <c r="P22" s="17">
         <f>C22+SUM(D22:O22)</f>
         <v/>
       </c>
-      <c r="R22" s="16">
+      <c r="R22" s="18">
         <f>IF(COUNT(D22:O22)=0,"",IF(ABS(P22-Gabarito!P22)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
@@ -1736,162 +1880,162 @@
           <t>Lucros Acumulados</t>
         </is>
       </c>
-      <c r="C23" s="14" t="n">
+      <c r="C23" s="16" t="n">
         <v>60</v>
       </c>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
-      <c r="I23" s="6" t="n"/>
-      <c r="J23" s="6" t="n"/>
-      <c r="K23" s="6" t="n"/>
-      <c r="L23" s="6" t="n"/>
-      <c r="M23" s="6" t="n"/>
-      <c r="N23" s="6" t="n"/>
-      <c r="O23" s="6" t="n"/>
-      <c r="P23" s="15">
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="9" t="n"/>
+      <c r="H23" s="9" t="n"/>
+      <c r="I23" s="9" t="n"/>
+      <c r="J23" s="9" t="n"/>
+      <c r="K23" s="9" t="n"/>
+      <c r="L23" s="9" t="n"/>
+      <c r="M23" s="9" t="n"/>
+      <c r="N23" s="9" t="n"/>
+      <c r="O23" s="9" t="n"/>
+      <c r="P23" s="17">
         <f>C23+SUM(D23:O23)</f>
         <v/>
       </c>
-      <c r="R23" s="16">
+      <c r="R23" s="18">
         <f>IF(COUNT(D23:O23)=0,"",IF(ABS(P23-Gabarito!P23)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>Total Passivo e Patrim. Líquido</t>
         </is>
       </c>
-      <c r="C24" s="18">
+      <c r="C24" s="20">
         <f>SUM(C14:C23)</f>
         <v/>
       </c>
-      <c r="D24" s="18">
+      <c r="D24" s="20">
         <f>SUM(D14:D23)</f>
         <v/>
       </c>
-      <c r="E24" s="18">
+      <c r="E24" s="20">
         <f>SUM(E14:E23)</f>
         <v/>
       </c>
-      <c r="F24" s="18">
+      <c r="F24" s="20">
         <f>SUM(F14:F23)</f>
         <v/>
       </c>
-      <c r="G24" s="18">
+      <c r="G24" s="20">
         <f>SUM(G14:G23)</f>
         <v/>
       </c>
-      <c r="H24" s="18">
+      <c r="H24" s="20">
         <f>SUM(H14:H23)</f>
         <v/>
       </c>
-      <c r="I24" s="18">
+      <c r="I24" s="20">
         <f>SUM(I14:I23)</f>
         <v/>
       </c>
-      <c r="J24" s="18">
+      <c r="J24" s="20">
         <f>SUM(J14:J23)</f>
         <v/>
       </c>
-      <c r="K24" s="18">
+      <c r="K24" s="20">
         <f>SUM(K14:K23)</f>
         <v/>
       </c>
-      <c r="L24" s="18">
+      <c r="L24" s="20">
         <f>SUM(L14:L23)</f>
         <v/>
       </c>
-      <c r="M24" s="18">
+      <c r="M24" s="20">
         <f>SUM(M14:M23)</f>
         <v/>
       </c>
-      <c r="N24" s="18">
+      <c r="N24" s="20">
         <f>SUM(N14:N23)</f>
         <v/>
       </c>
-      <c r="O24" s="18">
+      <c r="O24" s="20">
         <f>SUM(O14:O23)</f>
         <v/>
       </c>
-      <c r="P24" s="18">
+      <c r="P24" s="20">
         <f>SUM(P14:P23)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="19" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>Diferença, se houver (tem que dar zero)</t>
         </is>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="17">
         <f>C12-C24</f>
         <v/>
       </c>
-      <c r="D26" s="15">
+      <c r="D26" s="17">
         <f>D12-D24</f>
         <v/>
       </c>
-      <c r="E26" s="15">
+      <c r="E26" s="17">
         <f>E12-E24</f>
         <v/>
       </c>
-      <c r="F26" s="15">
+      <c r="F26" s="17">
         <f>F12-F24</f>
         <v/>
       </c>
-      <c r="G26" s="15">
+      <c r="G26" s="17">
         <f>G12-G24</f>
         <v/>
       </c>
-      <c r="H26" s="15">
+      <c r="H26" s="17">
         <f>H12-H24</f>
         <v/>
       </c>
-      <c r="I26" s="15">
+      <c r="I26" s="17">
         <f>I12-I24</f>
         <v/>
       </c>
-      <c r="J26" s="15">
+      <c r="J26" s="17">
         <f>J12-J24</f>
         <v/>
       </c>
-      <c r="K26" s="15">
+      <c r="K26" s="17">
         <f>K12-K24</f>
         <v/>
       </c>
-      <c r="L26" s="15">
+      <c r="L26" s="17">
         <f>L12-L24</f>
         <v/>
       </c>
-      <c r="M26" s="15">
+      <c r="M26" s="17">
         <f>M12-M24</f>
         <v/>
       </c>
-      <c r="N26" s="15">
+      <c r="N26" s="17">
         <f>N12-N24</f>
         <v/>
       </c>
-      <c r="O26" s="15">
+      <c r="O26" s="17">
         <f>O12-O24</f>
         <v/>
       </c>
-      <c r="P26" s="15">
+      <c r="P26" s="17">
         <f>P12-P24</f>
         <v/>
       </c>
-      <c r="R26" s="17">
+      <c r="R26" s="19">
         <f>IF(P26=0,"✔ fecha","✗ não fecha")</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>Demonstração do Resultado</t>
         </is>
@@ -1932,12 +2076,12 @@
       <c r="O28" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="P28" s="11" t="inlineStr">
+      <c r="P28" s="13" t="inlineStr">
         <is>
           <t>Ano 2</t>
         </is>
       </c>
-      <c r="R28" s="20" t="inlineStr">
+      <c r="R28" s="22" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
@@ -1949,23 +2093,23 @@
           <t>Receita Líquida de Vendas</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="n"/>
-      <c r="G29" s="6" t="n"/>
-      <c r="H29" s="6" t="n"/>
-      <c r="I29" s="6" t="n"/>
-      <c r="J29" s="6" t="n"/>
-      <c r="K29" s="6" t="n"/>
-      <c r="L29" s="6" t="n"/>
-      <c r="M29" s="6" t="n"/>
-      <c r="N29" s="6" t="n"/>
-      <c r="O29" s="6" t="n"/>
-      <c r="P29" s="15">
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="9" t="n"/>
+      <c r="G29" s="9" t="n"/>
+      <c r="H29" s="9" t="n"/>
+      <c r="I29" s="9" t="n"/>
+      <c r="J29" s="9" t="n"/>
+      <c r="K29" s="9" t="n"/>
+      <c r="L29" s="9" t="n"/>
+      <c r="M29" s="9" t="n"/>
+      <c r="N29" s="9" t="n"/>
+      <c r="O29" s="9" t="n"/>
+      <c r="P29" s="17">
         <f>SUM(D29:O29)</f>
         <v/>
       </c>
-      <c r="R29" s="16">
+      <c r="R29" s="18">
         <f>IF(COUNT(D29:O29)=0,"",IF(ABS(P29-Gabarito!P29)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
@@ -1976,82 +2120,82 @@
           <t>(-) Custo das Mercadorias Vendidas</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
-      <c r="E30" s="6" t="n"/>
-      <c r="F30" s="6" t="n"/>
-      <c r="G30" s="6" t="n"/>
-      <c r="H30" s="6" t="n"/>
-      <c r="I30" s="6" t="n"/>
-      <c r="J30" s="6" t="n"/>
-      <c r="K30" s="6" t="n"/>
-      <c r="L30" s="6" t="n"/>
-      <c r="M30" s="6" t="n"/>
-      <c r="N30" s="6" t="n"/>
-      <c r="O30" s="6" t="n"/>
-      <c r="P30" s="15">
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="9" t="n"/>
+      <c r="G30" s="9" t="n"/>
+      <c r="H30" s="9" t="n"/>
+      <c r="I30" s="9" t="n"/>
+      <c r="J30" s="9" t="n"/>
+      <c r="K30" s="9" t="n"/>
+      <c r="L30" s="9" t="n"/>
+      <c r="M30" s="9" t="n"/>
+      <c r="N30" s="9" t="n"/>
+      <c r="O30" s="9" t="n"/>
+      <c r="P30" s="17">
         <f>SUM(D30:O30)</f>
         <v/>
       </c>
-      <c r="R30" s="16">
+      <c r="R30" s="18">
         <f>IF(COUNT(D30:O30)=0,"",IF(ABS(P30-Gabarito!P30)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="17" t="inlineStr">
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">     (=) Lucro Bruto</t>
         </is>
       </c>
-      <c r="D31" s="18">
+      <c r="D31" s="20">
         <f>SUM(D29:D30)</f>
         <v/>
       </c>
-      <c r="E31" s="18">
+      <c r="E31" s="20">
         <f>SUM(E29:E30)</f>
         <v/>
       </c>
-      <c r="F31" s="18">
+      <c r="F31" s="20">
         <f>SUM(F29:F30)</f>
         <v/>
       </c>
-      <c r="G31" s="18">
+      <c r="G31" s="20">
         <f>SUM(G29:G30)</f>
         <v/>
       </c>
-      <c r="H31" s="18">
+      <c r="H31" s="20">
         <f>SUM(H29:H30)</f>
         <v/>
       </c>
-      <c r="I31" s="18">
+      <c r="I31" s="20">
         <f>SUM(I29:I30)</f>
         <v/>
       </c>
-      <c r="J31" s="18">
+      <c r="J31" s="20">
         <f>SUM(J29:J30)</f>
         <v/>
       </c>
-      <c r="K31" s="18">
+      <c r="K31" s="20">
         <f>SUM(K29:K30)</f>
         <v/>
       </c>
-      <c r="L31" s="18">
+      <c r="L31" s="20">
         <f>SUM(L29:L30)</f>
         <v/>
       </c>
-      <c r="M31" s="18">
+      <c r="M31" s="20">
         <f>SUM(M29:M30)</f>
         <v/>
       </c>
-      <c r="N31" s="18">
+      <c r="N31" s="20">
         <f>SUM(N29:N30)</f>
         <v/>
       </c>
-      <c r="O31" s="18">
+      <c r="O31" s="20">
         <f>SUM(O29:O30)</f>
         <v/>
       </c>
-      <c r="P31" s="18">
+      <c r="P31" s="20">
         <f>SUM(P29:P30)</f>
         <v/>
       </c>
@@ -2062,23 +2206,23 @@
           <t>(-) Despesas Operacionais</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n"/>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="6" t="n"/>
-      <c r="G32" s="6" t="n"/>
-      <c r="H32" s="6" t="n"/>
-      <c r="I32" s="6" t="n"/>
-      <c r="J32" s="6" t="n"/>
-      <c r="K32" s="6" t="n"/>
-      <c r="L32" s="6" t="n"/>
-      <c r="M32" s="6" t="n"/>
-      <c r="N32" s="6" t="n"/>
-      <c r="O32" s="6" t="n"/>
-      <c r="P32" s="15">
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="9" t="n"/>
+      <c r="G32" s="9" t="n"/>
+      <c r="H32" s="9" t="n"/>
+      <c r="I32" s="9" t="n"/>
+      <c r="J32" s="9" t="n"/>
+      <c r="K32" s="9" t="n"/>
+      <c r="L32" s="9" t="n"/>
+      <c r="M32" s="9" t="n"/>
+      <c r="N32" s="9" t="n"/>
+      <c r="O32" s="9" t="n"/>
+      <c r="P32" s="17">
         <f>SUM(D32:O32)</f>
         <v/>
       </c>
-      <c r="R32" s="16">
+      <c r="R32" s="18">
         <f>IF(COUNT(D32:O32)=0,"",IF(ABS(P32-Gabarito!P32)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
@@ -2089,82 +2233,82 @@
           <t>(-) Depreciação</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n"/>
-      <c r="E33" s="6" t="n"/>
-      <c r="F33" s="6" t="n"/>
-      <c r="G33" s="6" t="n"/>
-      <c r="H33" s="6" t="n"/>
-      <c r="I33" s="6" t="n"/>
-      <c r="J33" s="6" t="n"/>
-      <c r="K33" s="6" t="n"/>
-      <c r="L33" s="6" t="n"/>
-      <c r="M33" s="6" t="n"/>
-      <c r="N33" s="6" t="n"/>
-      <c r="O33" s="6" t="n"/>
-      <c r="P33" s="15">
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="9" t="n"/>
+      <c r="G33" s="9" t="n"/>
+      <c r="H33" s="9" t="n"/>
+      <c r="I33" s="9" t="n"/>
+      <c r="J33" s="9" t="n"/>
+      <c r="K33" s="9" t="n"/>
+      <c r="L33" s="9" t="n"/>
+      <c r="M33" s="9" t="n"/>
+      <c r="N33" s="9" t="n"/>
+      <c r="O33" s="9" t="n"/>
+      <c r="P33" s="17">
         <f>SUM(D33:O33)</f>
         <v/>
       </c>
-      <c r="R33" s="16">
+      <c r="R33" s="18">
         <f>IF(COUNT(D33:O33)=0,"",IF(ABS(P33-Gabarito!P33)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="17" t="inlineStr">
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">     (=) EBIT</t>
         </is>
       </c>
-      <c r="D34" s="18">
+      <c r="D34" s="20">
         <f>SUM(D31:D33)</f>
         <v/>
       </c>
-      <c r="E34" s="18">
+      <c r="E34" s="20">
         <f>SUM(E31:E33)</f>
         <v/>
       </c>
-      <c r="F34" s="18">
+      <c r="F34" s="20">
         <f>SUM(F31:F33)</f>
         <v/>
       </c>
-      <c r="G34" s="18">
+      <c r="G34" s="20">
         <f>SUM(G31:G33)</f>
         <v/>
       </c>
-      <c r="H34" s="18">
+      <c r="H34" s="20">
         <f>SUM(H31:H33)</f>
         <v/>
       </c>
-      <c r="I34" s="18">
+      <c r="I34" s="20">
         <f>SUM(I31:I33)</f>
         <v/>
       </c>
-      <c r="J34" s="18">
+      <c r="J34" s="20">
         <f>SUM(J31:J33)</f>
         <v/>
       </c>
-      <c r="K34" s="18">
+      <c r="K34" s="20">
         <f>SUM(K31:K33)</f>
         <v/>
       </c>
-      <c r="L34" s="18">
+      <c r="L34" s="20">
         <f>SUM(L31:L33)</f>
         <v/>
       </c>
-      <c r="M34" s="18">
+      <c r="M34" s="20">
         <f>SUM(M31:M33)</f>
         <v/>
       </c>
-      <c r="N34" s="18">
+      <c r="N34" s="20">
         <f>SUM(N31:N33)</f>
         <v/>
       </c>
-      <c r="O34" s="18">
+      <c r="O34" s="20">
         <f>SUM(O31:O33)</f>
         <v/>
       </c>
-      <c r="P34" s="18">
+      <c r="P34" s="20">
         <f>SUM(P31:P33)</f>
         <v/>
       </c>
@@ -2175,82 +2319,82 @@
           <t>(+/-) Resultado Financeiro</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n"/>
-      <c r="E35" s="6" t="n"/>
-      <c r="F35" s="6" t="n"/>
-      <c r="G35" s="6" t="n"/>
-      <c r="H35" s="6" t="n"/>
-      <c r="I35" s="6" t="n"/>
-      <c r="J35" s="6" t="n"/>
-      <c r="K35" s="6" t="n"/>
-      <c r="L35" s="6" t="n"/>
-      <c r="M35" s="6" t="n"/>
-      <c r="N35" s="6" t="n"/>
-      <c r="O35" s="6" t="n"/>
-      <c r="P35" s="15">
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="9" t="n"/>
+      <c r="I35" s="9" t="n"/>
+      <c r="J35" s="9" t="n"/>
+      <c r="K35" s="9" t="n"/>
+      <c r="L35" s="9" t="n"/>
+      <c r="M35" s="9" t="n"/>
+      <c r="N35" s="9" t="n"/>
+      <c r="O35" s="9" t="n"/>
+      <c r="P35" s="17">
         <f>SUM(D35:O35)</f>
         <v/>
       </c>
-      <c r="R35" s="16">
+      <c r="R35" s="18">
         <f>IF(COUNT(D35:O35)=0,"",IF(ABS(P35-Gabarito!P35)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="17" t="inlineStr">
+      <c r="B36" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">     (=) LAIR</t>
         </is>
       </c>
-      <c r="D36" s="18">
+      <c r="D36" s="20">
         <f>SUM(D34:D35)</f>
         <v/>
       </c>
-      <c r="E36" s="18">
+      <c r="E36" s="20">
         <f>SUM(E34:E35)</f>
         <v/>
       </c>
-      <c r="F36" s="18">
+      <c r="F36" s="20">
         <f>SUM(F34:F35)</f>
         <v/>
       </c>
-      <c r="G36" s="18">
+      <c r="G36" s="20">
         <f>SUM(G34:G35)</f>
         <v/>
       </c>
-      <c r="H36" s="18">
+      <c r="H36" s="20">
         <f>SUM(H34:H35)</f>
         <v/>
       </c>
-      <c r="I36" s="18">
+      <c r="I36" s="20">
         <f>SUM(I34:I35)</f>
         <v/>
       </c>
-      <c r="J36" s="18">
+      <c r="J36" s="20">
         <f>SUM(J34:J35)</f>
         <v/>
       </c>
-      <c r="K36" s="18">
+      <c r="K36" s="20">
         <f>SUM(K34:K35)</f>
         <v/>
       </c>
-      <c r="L36" s="18">
+      <c r="L36" s="20">
         <f>SUM(L34:L35)</f>
         <v/>
       </c>
-      <c r="M36" s="18">
+      <c r="M36" s="20">
         <f>SUM(M34:M35)</f>
         <v/>
       </c>
-      <c r="N36" s="18">
+      <c r="N36" s="20">
         <f>SUM(N34:N35)</f>
         <v/>
       </c>
-      <c r="O36" s="18">
+      <c r="O36" s="20">
         <f>SUM(O34:O35)</f>
         <v/>
       </c>
-      <c r="P36" s="18">
+      <c r="P36" s="20">
         <f>SUM(P34:P35)</f>
         <v/>
       </c>
@@ -2261,88 +2405,88 @@
           <t>(-) IR e CSLL</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n"/>
-      <c r="E37" s="6" t="n"/>
-      <c r="F37" s="6" t="n"/>
-      <c r="G37" s="6" t="n"/>
-      <c r="H37" s="6" t="n"/>
-      <c r="I37" s="6" t="n"/>
-      <c r="J37" s="6" t="n"/>
-      <c r="K37" s="6" t="n"/>
-      <c r="L37" s="6" t="n"/>
-      <c r="M37" s="6" t="n"/>
-      <c r="N37" s="6" t="n"/>
-      <c r="O37" s="6" t="n"/>
-      <c r="P37" s="15">
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="9" t="n"/>
+      <c r="I37" s="9" t="n"/>
+      <c r="J37" s="9" t="n"/>
+      <c r="K37" s="9" t="n"/>
+      <c r="L37" s="9" t="n"/>
+      <c r="M37" s="9" t="n"/>
+      <c r="N37" s="9" t="n"/>
+      <c r="O37" s="9" t="n"/>
+      <c r="P37" s="17">
         <f>SUM(D37:O37)</f>
         <v/>
       </c>
-      <c r="R37" s="16">
+      <c r="R37" s="18">
         <f>IF(COUNT(D37:O37)=0,"",IF(ABS(P37-Gabarito!P37)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="17" t="inlineStr">
+      <c r="B38" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">     (=) Lucro Líquido</t>
         </is>
       </c>
-      <c r="D38" s="18">
+      <c r="D38" s="20">
         <f>SUM(D36:D37)</f>
         <v/>
       </c>
-      <c r="E38" s="18">
+      <c r="E38" s="20">
         <f>SUM(E36:E37)</f>
         <v/>
       </c>
-      <c r="F38" s="18">
+      <c r="F38" s="20">
         <f>SUM(F36:F37)</f>
         <v/>
       </c>
-      <c r="G38" s="18">
+      <c r="G38" s="20">
         <f>SUM(G36:G37)</f>
         <v/>
       </c>
-      <c r="H38" s="18">
+      <c r="H38" s="20">
         <f>SUM(H36:H37)</f>
         <v/>
       </c>
-      <c r="I38" s="18">
+      <c r="I38" s="20">
         <f>SUM(I36:I37)</f>
         <v/>
       </c>
-      <c r="J38" s="18">
+      <c r="J38" s="20">
         <f>SUM(J36:J37)</f>
         <v/>
       </c>
-      <c r="K38" s="18">
+      <c r="K38" s="20">
         <f>SUM(K36:K37)</f>
         <v/>
       </c>
-      <c r="L38" s="18">
+      <c r="L38" s="20">
         <f>SUM(L36:L37)</f>
         <v/>
       </c>
-      <c r="M38" s="18">
+      <c r="M38" s="20">
         <f>SUM(M36:M37)</f>
         <v/>
       </c>
-      <c r="N38" s="18">
+      <c r="N38" s="20">
         <f>SUM(N36:N37)</f>
         <v/>
       </c>
-      <c r="O38" s="18">
+      <c r="O38" s="20">
         <f>SUM(O36:O37)</f>
         <v/>
       </c>
-      <c r="P38" s="18">
+      <c r="P38" s="20">
         <f>SUM(P36:P37)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B40" s="13" t="inlineStr">
         <is>
           <t>Demonstração dos Fluxos de Caixa</t>
         </is>
@@ -2383,67 +2527,67 @@
       <c r="O40" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="P40" s="11" t="inlineStr">
+      <c r="P40" s="13" t="inlineStr">
         <is>
           <t>Ano 2</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="17" t="inlineStr">
+      <c r="B41" s="19" t="inlineStr">
         <is>
           <t>OPERAÇÕES</t>
         </is>
       </c>
-      <c r="D41" s="18">
+      <c r="D41" s="20">
         <f>SUM(D42:D46)</f>
         <v/>
       </c>
-      <c r="E41" s="18">
+      <c r="E41" s="20">
         <f>SUM(E42:E46)</f>
         <v/>
       </c>
-      <c r="F41" s="18">
+      <c r="F41" s="20">
         <f>SUM(F42:F46)</f>
         <v/>
       </c>
-      <c r="G41" s="18">
+      <c r="G41" s="20">
         <f>SUM(G42:G46)</f>
         <v/>
       </c>
-      <c r="H41" s="18">
+      <c r="H41" s="20">
         <f>SUM(H42:H46)</f>
         <v/>
       </c>
-      <c r="I41" s="18">
+      <c r="I41" s="20">
         <f>SUM(I42:I46)</f>
         <v/>
       </c>
-      <c r="J41" s="18">
+      <c r="J41" s="20">
         <f>SUM(J42:J46)</f>
         <v/>
       </c>
-      <c r="K41" s="18">
+      <c r="K41" s="20">
         <f>SUM(K42:K46)</f>
         <v/>
       </c>
-      <c r="L41" s="18">
+      <c r="L41" s="20">
         <f>SUM(L42:L46)</f>
         <v/>
       </c>
-      <c r="M41" s="18">
+      <c r="M41" s="20">
         <f>SUM(M42:M46)</f>
         <v/>
       </c>
-      <c r="N41" s="18">
+      <c r="N41" s="20">
         <f>SUM(N42:N46)</f>
         <v/>
       </c>
-      <c r="O41" s="18">
+      <c r="O41" s="20">
         <f>SUM(O42:O46)</f>
         <v/>
       </c>
-      <c r="P41" s="18">
+      <c r="P41" s="20">
         <f>SUM(P42:P46)</f>
         <v/>
       </c>
@@ -2454,23 +2598,23 @@
           <t>Recebimentos de Clientes</t>
         </is>
       </c>
-      <c r="D42" s="6" t="n"/>
-      <c r="E42" s="6" t="n"/>
-      <c r="F42" s="6" t="n"/>
-      <c r="G42" s="6" t="n"/>
-      <c r="H42" s="6" t="n"/>
-      <c r="I42" s="6" t="n"/>
-      <c r="J42" s="6" t="n"/>
-      <c r="K42" s="6" t="n"/>
-      <c r="L42" s="6" t="n"/>
-      <c r="M42" s="6" t="n"/>
-      <c r="N42" s="6" t="n"/>
-      <c r="O42" s="6" t="n"/>
-      <c r="P42" s="15">
+      <c r="D42" s="9" t="n"/>
+      <c r="E42" s="9" t="n"/>
+      <c r="F42" s="9" t="n"/>
+      <c r="G42" s="9" t="n"/>
+      <c r="H42" s="9" t="n"/>
+      <c r="I42" s="9" t="n"/>
+      <c r="J42" s="9" t="n"/>
+      <c r="K42" s="9" t="n"/>
+      <c r="L42" s="9" t="n"/>
+      <c r="M42" s="9" t="n"/>
+      <c r="N42" s="9" t="n"/>
+      <c r="O42" s="9" t="n"/>
+      <c r="P42" s="17">
         <f>SUM(D42:O42)</f>
         <v/>
       </c>
-      <c r="R42" s="16">
+      <c r="R42" s="18">
         <f>IF(COUNT(D42:O42)=0,"",IF(ABS(P42-Gabarito!P42)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
@@ -2481,23 +2625,23 @@
           <t>Pagamentos a Fornecedores</t>
         </is>
       </c>
-      <c r="D43" s="6" t="n"/>
-      <c r="E43" s="6" t="n"/>
-      <c r="F43" s="6" t="n"/>
-      <c r="G43" s="6" t="n"/>
-      <c r="H43" s="6" t="n"/>
-      <c r="I43" s="6" t="n"/>
-      <c r="J43" s="6" t="n"/>
-      <c r="K43" s="6" t="n"/>
-      <c r="L43" s="6" t="n"/>
-      <c r="M43" s="6" t="n"/>
-      <c r="N43" s="6" t="n"/>
-      <c r="O43" s="6" t="n"/>
-      <c r="P43" s="15">
+      <c r="D43" s="9" t="n"/>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="9" t="n"/>
+      <c r="G43" s="9" t="n"/>
+      <c r="H43" s="9" t="n"/>
+      <c r="I43" s="9" t="n"/>
+      <c r="J43" s="9" t="n"/>
+      <c r="K43" s="9" t="n"/>
+      <c r="L43" s="9" t="n"/>
+      <c r="M43" s="9" t="n"/>
+      <c r="N43" s="9" t="n"/>
+      <c r="O43" s="9" t="n"/>
+      <c r="P43" s="17">
         <f>SUM(D43:O43)</f>
         <v/>
       </c>
-      <c r="R43" s="16">
+      <c r="R43" s="18">
         <f>IF(COUNT(D43:O43)=0,"",IF(ABS(P43-Gabarito!P43)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
@@ -2508,23 +2652,23 @@
           <t>Pagamentos de Despesas</t>
         </is>
       </c>
-      <c r="D44" s="6" t="n"/>
-      <c r="E44" s="6" t="n"/>
-      <c r="F44" s="6" t="n"/>
-      <c r="G44" s="6" t="n"/>
-      <c r="H44" s="6" t="n"/>
-      <c r="I44" s="6" t="n"/>
-      <c r="J44" s="6" t="n"/>
-      <c r="K44" s="6" t="n"/>
-      <c r="L44" s="6" t="n"/>
-      <c r="M44" s="6" t="n"/>
-      <c r="N44" s="6" t="n"/>
-      <c r="O44" s="6" t="n"/>
-      <c r="P44" s="15">
+      <c r="D44" s="9" t="n"/>
+      <c r="E44" s="9" t="n"/>
+      <c r="F44" s="9" t="n"/>
+      <c r="G44" s="9" t="n"/>
+      <c r="H44" s="9" t="n"/>
+      <c r="I44" s="9" t="n"/>
+      <c r="J44" s="9" t="n"/>
+      <c r="K44" s="9" t="n"/>
+      <c r="L44" s="9" t="n"/>
+      <c r="M44" s="9" t="n"/>
+      <c r="N44" s="9" t="n"/>
+      <c r="O44" s="9" t="n"/>
+      <c r="P44" s="17">
         <f>SUM(D44:O44)</f>
         <v/>
       </c>
-      <c r="R44" s="16">
+      <c r="R44" s="18">
         <f>IF(COUNT(D44:O44)=0,"",IF(ABS(P44-Gabarito!P44)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
@@ -2535,23 +2679,23 @@
           <t>Juros Pagos</t>
         </is>
       </c>
-      <c r="D45" s="6" t="n"/>
-      <c r="E45" s="6" t="n"/>
-      <c r="F45" s="6" t="n"/>
-      <c r="G45" s="6" t="n"/>
-      <c r="H45" s="6" t="n"/>
-      <c r="I45" s="6" t="n"/>
-      <c r="J45" s="6" t="n"/>
-      <c r="K45" s="6" t="n"/>
-      <c r="L45" s="6" t="n"/>
-      <c r="M45" s="6" t="n"/>
-      <c r="N45" s="6" t="n"/>
-      <c r="O45" s="6" t="n"/>
-      <c r="P45" s="15">
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="9" t="n"/>
+      <c r="G45" s="9" t="n"/>
+      <c r="H45" s="9" t="n"/>
+      <c r="I45" s="9" t="n"/>
+      <c r="J45" s="9" t="n"/>
+      <c r="K45" s="9" t="n"/>
+      <c r="L45" s="9" t="n"/>
+      <c r="M45" s="9" t="n"/>
+      <c r="N45" s="9" t="n"/>
+      <c r="O45" s="9" t="n"/>
+      <c r="P45" s="17">
         <f>SUM(D45:O45)</f>
         <v/>
       </c>
-      <c r="R45" s="16">
+      <c r="R45" s="18">
         <f>IF(COUNT(D45:O45)=0,"",IF(ABS(P45-Gabarito!P45)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
@@ -2562,82 +2706,82 @@
           <t>IR Pago</t>
         </is>
       </c>
-      <c r="D46" s="6" t="n"/>
-      <c r="E46" s="6" t="n"/>
-      <c r="F46" s="6" t="n"/>
-      <c r="G46" s="6" t="n"/>
-      <c r="H46" s="6" t="n"/>
-      <c r="I46" s="6" t="n"/>
-      <c r="J46" s="6" t="n"/>
-      <c r="K46" s="6" t="n"/>
-      <c r="L46" s="6" t="n"/>
-      <c r="M46" s="6" t="n"/>
-      <c r="N46" s="6" t="n"/>
-      <c r="O46" s="6" t="n"/>
-      <c r="P46" s="15">
+      <c r="D46" s="9" t="n"/>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="9" t="n"/>
+      <c r="G46" s="9" t="n"/>
+      <c r="H46" s="9" t="n"/>
+      <c r="I46" s="9" t="n"/>
+      <c r="J46" s="9" t="n"/>
+      <c r="K46" s="9" t="n"/>
+      <c r="L46" s="9" t="n"/>
+      <c r="M46" s="9" t="n"/>
+      <c r="N46" s="9" t="n"/>
+      <c r="O46" s="9" t="n"/>
+      <c r="P46" s="17">
         <f>SUM(D46:O46)</f>
         <v/>
       </c>
-      <c r="R46" s="16">
+      <c r="R46" s="18">
         <f>IF(COUNT(D46:O46)=0,"",IF(ABS(P46-Gabarito!P46)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="17" t="inlineStr">
+      <c r="B47" s="19" t="inlineStr">
         <is>
           <t>INVESTIMENTOS</t>
         </is>
       </c>
-      <c r="D47" s="18">
+      <c r="D47" s="20">
         <f>SUM(D48:D48)</f>
         <v/>
       </c>
-      <c r="E47" s="18">
+      <c r="E47" s="20">
         <f>SUM(E48:E48)</f>
         <v/>
       </c>
-      <c r="F47" s="18">
+      <c r="F47" s="20">
         <f>SUM(F48:F48)</f>
         <v/>
       </c>
-      <c r="G47" s="18">
+      <c r="G47" s="20">
         <f>SUM(G48:G48)</f>
         <v/>
       </c>
-      <c r="H47" s="18">
+      <c r="H47" s="20">
         <f>SUM(H48:H48)</f>
         <v/>
       </c>
-      <c r="I47" s="18">
+      <c r="I47" s="20">
         <f>SUM(I48:I48)</f>
         <v/>
       </c>
-      <c r="J47" s="18">
+      <c r="J47" s="20">
         <f>SUM(J48:J48)</f>
         <v/>
       </c>
-      <c r="K47" s="18">
+      <c r="K47" s="20">
         <f>SUM(K48:K48)</f>
         <v/>
       </c>
-      <c r="L47" s="18">
+      <c r="L47" s="20">
         <f>SUM(L48:L48)</f>
         <v/>
       </c>
-      <c r="M47" s="18">
+      <c r="M47" s="20">
         <f>SUM(M48:M48)</f>
         <v/>
       </c>
-      <c r="N47" s="18">
+      <c r="N47" s="20">
         <f>SUM(N48:N48)</f>
         <v/>
       </c>
-      <c r="O47" s="18">
+      <c r="O47" s="20">
         <f>SUM(O48:O48)</f>
         <v/>
       </c>
-      <c r="P47" s="18">
+      <c r="P47" s="20">
         <f>SUM(P48:P48)</f>
         <v/>
       </c>
@@ -2648,82 +2792,82 @@
           <t>Aquisição de Imobilizado</t>
         </is>
       </c>
-      <c r="D48" s="6" t="n"/>
-      <c r="E48" s="6" t="n"/>
-      <c r="F48" s="6" t="n"/>
-      <c r="G48" s="6" t="n"/>
-      <c r="H48" s="6" t="n"/>
-      <c r="I48" s="6" t="n"/>
-      <c r="J48" s="6" t="n"/>
-      <c r="K48" s="6" t="n"/>
-      <c r="L48" s="6" t="n"/>
-      <c r="M48" s="6" t="n"/>
-      <c r="N48" s="6" t="n"/>
-      <c r="O48" s="6" t="n"/>
-      <c r="P48" s="15">
+      <c r="D48" s="9" t="n"/>
+      <c r="E48" s="9" t="n"/>
+      <c r="F48" s="9" t="n"/>
+      <c r="G48" s="9" t="n"/>
+      <c r="H48" s="9" t="n"/>
+      <c r="I48" s="9" t="n"/>
+      <c r="J48" s="9" t="n"/>
+      <c r="K48" s="9" t="n"/>
+      <c r="L48" s="9" t="n"/>
+      <c r="M48" s="9" t="n"/>
+      <c r="N48" s="9" t="n"/>
+      <c r="O48" s="9" t="n"/>
+      <c r="P48" s="17">
         <f>SUM(D48:O48)</f>
         <v/>
       </c>
-      <c r="R48" s="16">
+      <c r="R48" s="18">
         <f>IF(COUNT(D48:O48)=0,"",IF(ABS(P48-Gabarito!P48)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="17" t="inlineStr">
+      <c r="B49" s="19" t="inlineStr">
         <is>
           <t>FINANCIAMENTOS</t>
         </is>
       </c>
-      <c r="D49" s="18">
+      <c r="D49" s="20">
         <f>SUM(D50:D52)</f>
         <v/>
       </c>
-      <c r="E49" s="18">
+      <c r="E49" s="20">
         <f>SUM(E50:E52)</f>
         <v/>
       </c>
-      <c r="F49" s="18">
+      <c r="F49" s="20">
         <f>SUM(F50:F52)</f>
         <v/>
       </c>
-      <c r="G49" s="18">
+      <c r="G49" s="20">
         <f>SUM(G50:G52)</f>
         <v/>
       </c>
-      <c r="H49" s="18">
+      <c r="H49" s="20">
         <f>SUM(H50:H52)</f>
         <v/>
       </c>
-      <c r="I49" s="18">
+      <c r="I49" s="20">
         <f>SUM(I50:I52)</f>
         <v/>
       </c>
-      <c r="J49" s="18">
+      <c r="J49" s="20">
         <f>SUM(J50:J52)</f>
         <v/>
       </c>
-      <c r="K49" s="18">
+      <c r="K49" s="20">
         <f>SUM(K50:K52)</f>
         <v/>
       </c>
-      <c r="L49" s="18">
+      <c r="L49" s="20">
         <f>SUM(L50:L52)</f>
         <v/>
       </c>
-      <c r="M49" s="18">
+      <c r="M49" s="20">
         <f>SUM(M50:M52)</f>
         <v/>
       </c>
-      <c r="N49" s="18">
+      <c r="N49" s="20">
         <f>SUM(N50:N52)</f>
         <v/>
       </c>
-      <c r="O49" s="18">
+      <c r="O49" s="20">
         <f>SUM(O50:O52)</f>
         <v/>
       </c>
-      <c r="P49" s="18">
+      <c r="P49" s="20">
         <f>SUM(P50:P52)</f>
         <v/>
       </c>
@@ -2734,23 +2878,23 @@
           <t>Captação de Empréstimos</t>
         </is>
       </c>
-      <c r="D50" s="6" t="n"/>
-      <c r="E50" s="6" t="n"/>
-      <c r="F50" s="6" t="n"/>
-      <c r="G50" s="6" t="n"/>
-      <c r="H50" s="6" t="n"/>
-      <c r="I50" s="6" t="n"/>
-      <c r="J50" s="6" t="n"/>
-      <c r="K50" s="6" t="n"/>
-      <c r="L50" s="6" t="n"/>
-      <c r="M50" s="6" t="n"/>
-      <c r="N50" s="6" t="n"/>
-      <c r="O50" s="6" t="n"/>
-      <c r="P50" s="15">
+      <c r="D50" s="9" t="n"/>
+      <c r="E50" s="9" t="n"/>
+      <c r="F50" s="9" t="n"/>
+      <c r="G50" s="9" t="n"/>
+      <c r="H50" s="9" t="n"/>
+      <c r="I50" s="9" t="n"/>
+      <c r="J50" s="9" t="n"/>
+      <c r="K50" s="9" t="n"/>
+      <c r="L50" s="9" t="n"/>
+      <c r="M50" s="9" t="n"/>
+      <c r="N50" s="9" t="n"/>
+      <c r="O50" s="9" t="n"/>
+      <c r="P50" s="17">
         <f>SUM(D50:O50)</f>
         <v/>
       </c>
-      <c r="R50" s="16">
+      <c r="R50" s="18">
         <f>IF(COUNT(D50:O50)=0,"",IF(ABS(P50-Gabarito!P50)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
@@ -2761,23 +2905,23 @@
           <t>Amortização de Empréstimos</t>
         </is>
       </c>
-      <c r="D51" s="6" t="n"/>
-      <c r="E51" s="6" t="n"/>
-      <c r="F51" s="6" t="n"/>
-      <c r="G51" s="6" t="n"/>
-      <c r="H51" s="6" t="n"/>
-      <c r="I51" s="6" t="n"/>
-      <c r="J51" s="6" t="n"/>
-      <c r="K51" s="6" t="n"/>
-      <c r="L51" s="6" t="n"/>
-      <c r="M51" s="6" t="n"/>
-      <c r="N51" s="6" t="n"/>
-      <c r="O51" s="6" t="n"/>
-      <c r="P51" s="15">
+      <c r="D51" s="9" t="n"/>
+      <c r="E51" s="9" t="n"/>
+      <c r="F51" s="9" t="n"/>
+      <c r="G51" s="9" t="n"/>
+      <c r="H51" s="9" t="n"/>
+      <c r="I51" s="9" t="n"/>
+      <c r="J51" s="9" t="n"/>
+      <c r="K51" s="9" t="n"/>
+      <c r="L51" s="9" t="n"/>
+      <c r="M51" s="9" t="n"/>
+      <c r="N51" s="9" t="n"/>
+      <c r="O51" s="9" t="n"/>
+      <c r="P51" s="17">
         <f>SUM(D51:O51)</f>
         <v/>
       </c>
-      <c r="R51" s="16">
+      <c r="R51" s="18">
         <f>IF(COUNT(D51:O51)=0,"",IF(ABS(P51-Gabarito!P51)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
@@ -2788,82 +2932,82 @@
           <t>Dividendos Pagos</t>
         </is>
       </c>
-      <c r="D52" s="6" t="n"/>
-      <c r="E52" s="6" t="n"/>
-      <c r="F52" s="6" t="n"/>
-      <c r="G52" s="6" t="n"/>
-      <c r="H52" s="6" t="n"/>
-      <c r="I52" s="6" t="n"/>
-      <c r="J52" s="6" t="n"/>
-      <c r="K52" s="6" t="n"/>
-      <c r="L52" s="6" t="n"/>
-      <c r="M52" s="6" t="n"/>
-      <c r="N52" s="6" t="n"/>
-      <c r="O52" s="6" t="n"/>
-      <c r="P52" s="15">
+      <c r="D52" s="9" t="n"/>
+      <c r="E52" s="9" t="n"/>
+      <c r="F52" s="9" t="n"/>
+      <c r="G52" s="9" t="n"/>
+      <c r="H52" s="9" t="n"/>
+      <c r="I52" s="9" t="n"/>
+      <c r="J52" s="9" t="n"/>
+      <c r="K52" s="9" t="n"/>
+      <c r="L52" s="9" t="n"/>
+      <c r="M52" s="9" t="n"/>
+      <c r="N52" s="9" t="n"/>
+      <c r="O52" s="9" t="n"/>
+      <c r="P52" s="17">
         <f>SUM(D52:O52)</f>
         <v/>
       </c>
-      <c r="R52" s="16">
+      <c r="R52" s="18">
         <f>IF(COUNT(D52:O52)=0,"",IF(ABS(P52-Gabarito!P52)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="17" t="inlineStr">
+      <c r="B53" s="19" t="inlineStr">
         <is>
           <t>VARIAÇÃO NO CAIXA</t>
         </is>
       </c>
-      <c r="D53" s="18">
+      <c r="D53" s="20">
         <f>D41+D47+D49</f>
         <v/>
       </c>
-      <c r="E53" s="18">
+      <c r="E53" s="20">
         <f>E41+E47+E49</f>
         <v/>
       </c>
-      <c r="F53" s="18">
+      <c r="F53" s="20">
         <f>F41+F47+F49</f>
         <v/>
       </c>
-      <c r="G53" s="18">
+      <c r="G53" s="20">
         <f>G41+G47+G49</f>
         <v/>
       </c>
-      <c r="H53" s="18">
+      <c r="H53" s="20">
         <f>H41+H47+H49</f>
         <v/>
       </c>
-      <c r="I53" s="18">
+      <c r="I53" s="20">
         <f>I41+I47+I49</f>
         <v/>
       </c>
-      <c r="J53" s="18">
+      <c r="J53" s="20">
         <f>J41+J47+J49</f>
         <v/>
       </c>
-      <c r="K53" s="18">
+      <c r="K53" s="20">
         <f>K41+K47+K49</f>
         <v/>
       </c>
-      <c r="L53" s="18">
+      <c r="L53" s="20">
         <f>L41+L47+L49</f>
         <v/>
       </c>
-      <c r="M53" s="18">
+      <c r="M53" s="20">
         <f>M41+M47+M49</f>
         <v/>
       </c>
-      <c r="N53" s="18">
+      <c r="N53" s="20">
         <f>N41+N47+N49</f>
         <v/>
       </c>
-      <c r="O53" s="18">
+      <c r="O53" s="20">
         <f>O41+O47+O49</f>
         <v/>
       </c>
-      <c r="P53" s="18">
+      <c r="P53" s="20">
         <f>P41+P47+P49</f>
         <v/>
       </c>
@@ -2874,38 +3018,38 @@
           <t xml:space="preserve">    Saldo inicial de caixa</t>
         </is>
       </c>
-      <c r="P54" s="14" t="n">
+      <c r="P54" s="16" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="17" t="inlineStr">
+      <c r="B55" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    Saldo final de caixa</t>
         </is>
       </c>
-      <c r="P55" s="15">
+      <c r="P55" s="17">
         <f>P54+P53</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="19" t="inlineStr">
+      <c r="B57" s="21" t="inlineStr">
         <is>
           <t>Caixa final da DFC menos Caixa do BP (tem que dar zero)</t>
         </is>
       </c>
-      <c r="P57" s="15">
+      <c r="P57" s="17">
         <f>P55-P6</f>
         <v/>
       </c>
-      <c r="R57" s="17">
+      <c r="R57" s="19">
         <f>IF(P57=0,"✔ amarra","✗ não amarra")</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="11" t="inlineStr">
+      <c r="B59" s="13" t="inlineStr">
         <is>
           <t>Indicadores (automáticos)</t>
         </is>
@@ -2917,7 +3061,7 @@
           <t>Margem bruta</t>
         </is>
       </c>
-      <c r="P60" s="21">
+      <c r="P60" s="23">
         <f>IF(P29=0,"",P31/P29)</f>
         <v/>
       </c>
@@ -2928,7 +3072,7 @@
           <t>Margem líquida</t>
         </is>
       </c>
-      <c r="P61" s="21">
+      <c r="P61" s="23">
         <f>IF(P29=0,"",P38/P29)</f>
         <v/>
       </c>
@@ -2939,7 +3083,7 @@
           <t>% financiado por capital próprio (PL / Ativo)</t>
         </is>
       </c>
-      <c r="P62" s="21">
+      <c r="P62" s="23">
         <f>IF(P12=0,"",SUM(P22:P23)/P12)</f>
         <v/>
       </c>
@@ -2950,7 +3094,7 @@
           <t>ROE (LL / PL final)</t>
         </is>
       </c>
-      <c r="P63" s="21">
+      <c r="P63" s="23">
         <f>IF(SUM(P22:P23)=0,"",P38/SUM(P22:P23))</f>
         <v/>
       </c>
@@ -2995,81 +3139,81 @@
           <t>Cervejaria Mar Grosso S.A.  |  Ano 2  |  valores em R$ mil</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Transações, por Número e Descrição</t>
         </is>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>Vendas do ano de 520, sendo 380 à vista e 140 a prazo; o cus</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>Compras de estoque no ano: 330, integralmente a prazo</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>Recebimento de 95 de clientes, referente a vendas de anos an</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>Pagamento de 310 a fornecedores</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>Cliente corporativo adianta 25 por uma encomenda que só será</t>
         </is>
       </c>
-      <c r="I2" s="10" t="inlineStr">
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>Despesas de vendas e administrativas de 90, pagas à vista</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr">
+      <c r="J2" s="12" t="inlineStr">
         <is>
           <t>Depreciação do imobilizado no ano: 30</t>
         </is>
       </c>
-      <c r="K2" s="10" t="inlineStr">
+      <c r="K2" s="12" t="inlineStr">
         <is>
           <t>Captação de novo empréstimo bancário de 80</t>
         </is>
       </c>
-      <c r="L2" s="10" t="inlineStr">
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>Amortização de 50 do principal da dívida e pagamento de 10 d</t>
         </is>
       </c>
-      <c r="M2" s="10" t="inlineStr">
+      <c r="M2" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Compra de um novo forno por 120, pagando 45 à vista e 75 em </t>
         </is>
       </c>
-      <c r="N2" s="10" t="inlineStr">
+      <c r="N2" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">IR e CSLL do ano: 27, sendo 20 pagos à vista e 7 a recolher </t>
         </is>
       </c>
-      <c r="O2" s="10" t="inlineStr">
+      <c r="O2" s="12" t="inlineStr">
         <is>
           <t>Dividendos de 25 declarados e pagos em dinheiro</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Balanço Patrimonial</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Balanço Inicial</t>
         </is>
@@ -3110,21 +3254,21 @@
       <c r="O3" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="P3" s="11" t="inlineStr">
+      <c r="P3" s="13" t="inlineStr">
         <is>
           <t>Balanço Final</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>ATIVO</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>Ativo Circulante</t>
         </is>
@@ -3136,42 +3280,42 @@
           <t>Caixa</t>
         </is>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="16" t="n">
         <v>40</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="9" t="n">
         <v>380</v>
       </c>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n">
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n">
         <v>95</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="9" t="n">
         <v>-310</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="9" t="n">
         <v>-90</v>
       </c>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="6" t="n">
+      <c r="J6" s="9" t="n"/>
+      <c r="K6" s="9" t="n">
         <v>80</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="L6" s="9" t="n">
         <v>-60</v>
       </c>
-      <c r="M6" s="6" t="n">
+      <c r="M6" s="9" t="n">
         <v>-45</v>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="N6" s="9" t="n">
         <v>-20</v>
       </c>
-      <c r="O6" s="6" t="n">
+      <c r="O6" s="9" t="n">
         <v>-25</v>
       </c>
-      <c r="P6" s="15">
+      <c r="P6" s="17">
         <f>C6+SUM(D6:O6)</f>
         <v/>
       </c>
@@ -3182,26 +3326,26 @@
           <t>Contas a Receber</t>
         </is>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="16" t="n">
         <v>60</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="9" t="n">
         <v>140</v>
       </c>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n">
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="9" t="n">
         <v>-95</v>
       </c>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-      <c r="M7" s="6" t="n"/>
-      <c r="N7" s="6" t="n"/>
-      <c r="O7" s="6" t="n"/>
-      <c r="P7" s="15">
+      <c r="G7" s="9" t="n"/>
+      <c r="H7" s="9" t="n"/>
+      <c r="I7" s="9" t="n"/>
+      <c r="J7" s="9" t="n"/>
+      <c r="K7" s="9" t="n"/>
+      <c r="L7" s="9" t="n"/>
+      <c r="M7" s="9" t="n"/>
+      <c r="N7" s="9" t="n"/>
+      <c r="O7" s="9" t="n"/>
+      <c r="P7" s="17">
         <f>C7+SUM(D7:O7)</f>
         <v/>
       </c>
@@ -3212,32 +3356,32 @@
           <t>Estoques</t>
         </is>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="16" t="n">
         <v>90</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="9" t="n">
         <v>-300</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="9" t="n">
         <v>330</v>
       </c>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
-      <c r="M8" s="6" t="n"/>
-      <c r="N8" s="6" t="n"/>
-      <c r="O8" s="6" t="n"/>
-      <c r="P8" s="15">
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="9" t="n"/>
+      <c r="H8" s="9" t="n"/>
+      <c r="I8" s="9" t="n"/>
+      <c r="J8" s="9" t="n"/>
+      <c r="K8" s="9" t="n"/>
+      <c r="L8" s="9" t="n"/>
+      <c r="M8" s="9" t="n"/>
+      <c r="N8" s="9" t="n"/>
+      <c r="O8" s="9" t="n"/>
+      <c r="P8" s="17">
         <f>C8+SUM(D8:O8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Ativo Não Circulante</t>
         </is>
@@ -3249,24 +3393,24 @@
           <t>Imobilizado</t>
         </is>
       </c>
-      <c r="C10" s="14" t="n">
+      <c r="C10" s="16" t="n">
         <v>300</v>
       </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="6" t="n"/>
-      <c r="M10" s="6" t="n">
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="9" t="n"/>
+      <c r="I10" s="9" t="n"/>
+      <c r="J10" s="9" t="n"/>
+      <c r="K10" s="9" t="n"/>
+      <c r="L10" s="9" t="n"/>
+      <c r="M10" s="9" t="n">
         <v>120</v>
       </c>
-      <c r="N10" s="6" t="n"/>
-      <c r="O10" s="6" t="n"/>
-      <c r="P10" s="15">
+      <c r="N10" s="9" t="n"/>
+      <c r="O10" s="9" t="n"/>
+      <c r="P10" s="17">
         <f>C10+SUM(D10:O10)</f>
         <v/>
       </c>
@@ -3277,100 +3421,100 @@
           <t>(-) Depreciação Acumulada</t>
         </is>
       </c>
-      <c r="C11" s="14" t="n">
+      <c r="C11" s="16" t="n">
         <v>-60</v>
       </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n">
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="9" t="n"/>
+      <c r="I11" s="9" t="n"/>
+      <c r="J11" s="9" t="n">
         <v>-30</v>
       </c>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="6" t="n"/>
-      <c r="M11" s="6" t="n"/>
-      <c r="N11" s="6" t="n"/>
-      <c r="O11" s="6" t="n"/>
-      <c r="P11" s="15">
+      <c r="K11" s="9" t="n"/>
+      <c r="L11" s="9" t="n"/>
+      <c r="M11" s="9" t="n"/>
+      <c r="N11" s="9" t="n"/>
+      <c r="O11" s="9" t="n"/>
+      <c r="P11" s="17">
         <f>C11+SUM(D11:O11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  Total do Ativo</t>
         </is>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="20">
         <f>SUM(C6:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="20">
         <f>SUM(D6:D11)</f>
         <v/>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="20">
         <f>SUM(E6:E11)</f>
         <v/>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="20">
         <f>SUM(F6:F11)</f>
         <v/>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="20">
         <f>SUM(G6:G11)</f>
         <v/>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="20">
         <f>SUM(H6:H11)</f>
         <v/>
       </c>
-      <c r="I12" s="18">
+      <c r="I12" s="20">
         <f>SUM(I6:I11)</f>
         <v/>
       </c>
-      <c r="J12" s="18">
+      <c r="J12" s="20">
         <f>SUM(J6:J11)</f>
         <v/>
       </c>
-      <c r="K12" s="18">
+      <c r="K12" s="20">
         <f>SUM(K6:K11)</f>
         <v/>
       </c>
-      <c r="L12" s="18">
+      <c r="L12" s="20">
         <f>SUM(L6:L11)</f>
         <v/>
       </c>
-      <c r="M12" s="18">
+      <c r="M12" s="20">
         <f>SUM(M6:M11)</f>
         <v/>
       </c>
-      <c r="N12" s="18">
+      <c r="N12" s="20">
         <f>SUM(N6:N11)</f>
         <v/>
       </c>
-      <c r="O12" s="18">
+      <c r="O12" s="20">
         <f>SUM(O6:O11)</f>
         <v/>
       </c>
-      <c r="P12" s="18">
+      <c r="P12" s="20">
         <f>SUM(P6:P11)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>PASSIVO E PATRIM. LÍQUIDO</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>Passivo Circulante:</t>
         </is>
@@ -3382,26 +3526,26 @@
           <t>Fornecedores</t>
         </is>
       </c>
-      <c r="C15" s="14" t="n">
+      <c r="C15" s="16" t="n">
         <v>70</v>
       </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n">
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n">
         <v>330</v>
       </c>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n">
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n">
         <v>-310</v>
       </c>
-      <c r="H15" s="6" t="n"/>
-      <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="6" t="n"/>
-      <c r="M15" s="6" t="n"/>
-      <c r="N15" s="6" t="n"/>
-      <c r="O15" s="6" t="n"/>
-      <c r="P15" s="15">
+      <c r="H15" s="9" t="n"/>
+      <c r="I15" s="9" t="n"/>
+      <c r="J15" s="9" t="n"/>
+      <c r="K15" s="9" t="n"/>
+      <c r="L15" s="9" t="n"/>
+      <c r="M15" s="9" t="n"/>
+      <c r="N15" s="9" t="n"/>
+      <c r="O15" s="9" t="n"/>
+      <c r="P15" s="17">
         <f>C15+SUM(D15:O15)</f>
         <v/>
       </c>
@@ -3412,22 +3556,22 @@
           <t>Adiantamentos de Clientes</t>
         </is>
       </c>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n">
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="6" t="n"/>
-      <c r="L16" s="6" t="n"/>
-      <c r="M16" s="6" t="n"/>
-      <c r="N16" s="6" t="n"/>
-      <c r="O16" s="6" t="n"/>
-      <c r="P16" s="15">
+      <c r="I16" s="9" t="n"/>
+      <c r="J16" s="9" t="n"/>
+      <c r="K16" s="9" t="n"/>
+      <c r="L16" s="9" t="n"/>
+      <c r="M16" s="9" t="n"/>
+      <c r="N16" s="9" t="n"/>
+      <c r="O16" s="9" t="n"/>
+      <c r="P16" s="17">
         <f>C16+SUM(D16:O16)</f>
         <v/>
       </c>
@@ -3438,22 +3582,22 @@
           <t>IR a Pagar</t>
         </is>
       </c>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
-      <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="6" t="n"/>
-      <c r="L17" s="6" t="n"/>
-      <c r="M17" s="6" t="n"/>
-      <c r="N17" s="6" t="n">
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="9" t="n"/>
+      <c r="I17" s="9" t="n"/>
+      <c r="J17" s="9" t="n"/>
+      <c r="K17" s="9" t="n"/>
+      <c r="L17" s="9" t="n"/>
+      <c r="M17" s="9" t="n"/>
+      <c r="N17" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="O17" s="6" t="n"/>
-      <c r="P17" s="15">
+      <c r="O17" s="9" t="n"/>
+      <c r="P17" s="17">
         <f>C17+SUM(D17:O17)</f>
         <v/>
       </c>
@@ -3464,32 +3608,32 @@
           <t>Empréstimos</t>
         </is>
       </c>
-      <c r="C18" s="14" t="n">
+      <c r="C18" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
-      <c r="I18" s="6" t="n"/>
-      <c r="J18" s="6" t="n"/>
-      <c r="K18" s="6" t="n">
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="9" t="n"/>
+      <c r="H18" s="9" t="n"/>
+      <c r="I18" s="9" t="n"/>
+      <c r="J18" s="9" t="n"/>
+      <c r="K18" s="9" t="n">
         <v>80</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="L18" s="9" t="n">
         <v>-50</v>
       </c>
-      <c r="M18" s="6" t="n"/>
-      <c r="N18" s="6" t="n"/>
-      <c r="O18" s="6" t="n"/>
-      <c r="P18" s="15">
+      <c r="M18" s="9" t="n"/>
+      <c r="N18" s="9" t="n"/>
+      <c r="O18" s="9" t="n"/>
+      <c r="P18" s="17">
         <f>C18+SUM(D18:O18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>Passivo Não Circulante:</t>
         </is>
@@ -3501,28 +3645,28 @@
           <t>Financiamento a Pagar (LP)</t>
         </is>
       </c>
-      <c r="C20" s="14" t="n"/>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
-      <c r="I20" s="6" t="n"/>
-      <c r="J20" s="6" t="n"/>
-      <c r="K20" s="6" t="n"/>
-      <c r="L20" s="6" t="n"/>
-      <c r="M20" s="6" t="n">
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="9" t="n"/>
+      <c r="H20" s="9" t="n"/>
+      <c r="I20" s="9" t="n"/>
+      <c r="J20" s="9" t="n"/>
+      <c r="K20" s="9" t="n"/>
+      <c r="L20" s="9" t="n"/>
+      <c r="M20" s="9" t="n">
         <v>75</v>
       </c>
-      <c r="N20" s="6" t="n"/>
-      <c r="O20" s="6" t="n"/>
-      <c r="P20" s="15">
+      <c r="N20" s="9" t="n"/>
+      <c r="O20" s="9" t="n"/>
+      <c r="P20" s="17">
         <f>C20+SUM(D20:O20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>Patrimônio Líquido:</t>
         </is>
@@ -3534,22 +3678,22 @@
           <t>Capital Social</t>
         </is>
       </c>
-      <c r="C22" s="14" t="n">
+      <c r="C22" s="16" t="n">
         <v>200</v>
       </c>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
-      <c r="I22" s="6" t="n"/>
-      <c r="J22" s="6" t="n"/>
-      <c r="K22" s="6" t="n"/>
-      <c r="L22" s="6" t="n"/>
-      <c r="M22" s="6" t="n"/>
-      <c r="N22" s="6" t="n"/>
-      <c r="O22" s="6" t="n"/>
-      <c r="P22" s="15">
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="9" t="n"/>
+      <c r="G22" s="9" t="n"/>
+      <c r="H22" s="9" t="n"/>
+      <c r="I22" s="9" t="n"/>
+      <c r="J22" s="9" t="n"/>
+      <c r="K22" s="9" t="n"/>
+      <c r="L22" s="9" t="n"/>
+      <c r="M22" s="9" t="n"/>
+      <c r="N22" s="9" t="n"/>
+      <c r="O22" s="9" t="n"/>
+      <c r="P22" s="17">
         <f>C22+SUM(D22:O22)</f>
         <v/>
       </c>
@@ -3560,166 +3704,166 @@
           <t>Lucros Acumulados</t>
         </is>
       </c>
-      <c r="C23" s="14" t="n">
+      <c r="C23" s="16" t="n">
         <v>60</v>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="9" t="n">
         <v>220</v>
       </c>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
-      <c r="I23" s="6" t="n">
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="9" t="n"/>
+      <c r="H23" s="9" t="n"/>
+      <c r="I23" s="9" t="n">
         <v>-90</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="J23" s="9" t="n">
         <v>-30</v>
       </c>
-      <c r="K23" s="6" t="n"/>
-      <c r="L23" s="6" t="n">
+      <c r="K23" s="9" t="n"/>
+      <c r="L23" s="9" t="n">
         <v>-10</v>
       </c>
-      <c r="M23" s="6" t="n"/>
-      <c r="N23" s="6" t="n">
+      <c r="M23" s="9" t="n"/>
+      <c r="N23" s="9" t="n">
         <v>-27</v>
       </c>
-      <c r="O23" s="6" t="n">
+      <c r="O23" s="9" t="n">
         <v>-25</v>
       </c>
-      <c r="P23" s="15">
+      <c r="P23" s="17">
         <f>C23+SUM(D23:O23)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>Total Passivo e Patrim. Líquido</t>
         </is>
       </c>
-      <c r="C24" s="18">
+      <c r="C24" s="20">
         <f>SUM(C14:C23)</f>
         <v/>
       </c>
-      <c r="D24" s="18">
+      <c r="D24" s="20">
         <f>SUM(D14:D23)</f>
         <v/>
       </c>
-      <c r="E24" s="18">
+      <c r="E24" s="20">
         <f>SUM(E14:E23)</f>
         <v/>
       </c>
-      <c r="F24" s="18">
+      <c r="F24" s="20">
         <f>SUM(F14:F23)</f>
         <v/>
       </c>
-      <c r="G24" s="18">
+      <c r="G24" s="20">
         <f>SUM(G14:G23)</f>
         <v/>
       </c>
-      <c r="H24" s="18">
+      <c r="H24" s="20">
         <f>SUM(H14:H23)</f>
         <v/>
       </c>
-      <c r="I24" s="18">
+      <c r="I24" s="20">
         <f>SUM(I14:I23)</f>
         <v/>
       </c>
-      <c r="J24" s="18">
+      <c r="J24" s="20">
         <f>SUM(J14:J23)</f>
         <v/>
       </c>
-      <c r="K24" s="18">
+      <c r="K24" s="20">
         <f>SUM(K14:K23)</f>
         <v/>
       </c>
-      <c r="L24" s="18">
+      <c r="L24" s="20">
         <f>SUM(L14:L23)</f>
         <v/>
       </c>
-      <c r="M24" s="18">
+      <c r="M24" s="20">
         <f>SUM(M14:M23)</f>
         <v/>
       </c>
-      <c r="N24" s="18">
+      <c r="N24" s="20">
         <f>SUM(N14:N23)</f>
         <v/>
       </c>
-      <c r="O24" s="18">
+      <c r="O24" s="20">
         <f>SUM(O14:O23)</f>
         <v/>
       </c>
-      <c r="P24" s="18">
+      <c r="P24" s="20">
         <f>SUM(P14:P23)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="19" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>Diferença, se houver (tem que dar zero)</t>
         </is>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="17">
         <f>C12-C24</f>
         <v/>
       </c>
-      <c r="D26" s="15">
+      <c r="D26" s="17">
         <f>D12-D24</f>
         <v/>
       </c>
-      <c r="E26" s="15">
+      <c r="E26" s="17">
         <f>E12-E24</f>
         <v/>
       </c>
-      <c r="F26" s="15">
+      <c r="F26" s="17">
         <f>F12-F24</f>
         <v/>
       </c>
-      <c r="G26" s="15">
+      <c r="G26" s="17">
         <f>G12-G24</f>
         <v/>
       </c>
-      <c r="H26" s="15">
+      <c r="H26" s="17">
         <f>H12-H24</f>
         <v/>
       </c>
-      <c r="I26" s="15">
+      <c r="I26" s="17">
         <f>I12-I24</f>
         <v/>
       </c>
-      <c r="J26" s="15">
+      <c r="J26" s="17">
         <f>J12-J24</f>
         <v/>
       </c>
-      <c r="K26" s="15">
+      <c r="K26" s="17">
         <f>K12-K24</f>
         <v/>
       </c>
-      <c r="L26" s="15">
+      <c r="L26" s="17">
         <f>L12-L24</f>
         <v/>
       </c>
-      <c r="M26" s="15">
+      <c r="M26" s="17">
         <f>M12-M24</f>
         <v/>
       </c>
-      <c r="N26" s="15">
+      <c r="N26" s="17">
         <f>N12-N24</f>
         <v/>
       </c>
-      <c r="O26" s="15">
+      <c r="O26" s="17">
         <f>O12-O24</f>
         <v/>
       </c>
-      <c r="P26" s="15">
+      <c r="P26" s="17">
         <f>P12-P24</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>Demonstração do Resultado</t>
         </is>
@@ -3760,12 +3904,12 @@
       <c r="O28" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="P28" s="11" t="inlineStr">
+      <c r="P28" s="13" t="inlineStr">
         <is>
           <t>Ano 2</t>
         </is>
       </c>
-      <c r="R28" s="20" t="inlineStr">
+      <c r="R28" s="22" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
@@ -3777,21 +3921,21 @@
           <t>Receita Líquida de Vendas</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="9" t="n">
         <v>520</v>
       </c>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="n"/>
-      <c r="G29" s="6" t="n"/>
-      <c r="H29" s="6" t="n"/>
-      <c r="I29" s="6" t="n"/>
-      <c r="J29" s="6" t="n"/>
-      <c r="K29" s="6" t="n"/>
-      <c r="L29" s="6" t="n"/>
-      <c r="M29" s="6" t="n"/>
-      <c r="N29" s="6" t="n"/>
-      <c r="O29" s="6" t="n"/>
-      <c r="P29" s="15">
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="9" t="n"/>
+      <c r="G29" s="9" t="n"/>
+      <c r="H29" s="9" t="n"/>
+      <c r="I29" s="9" t="n"/>
+      <c r="J29" s="9" t="n"/>
+      <c r="K29" s="9" t="n"/>
+      <c r="L29" s="9" t="n"/>
+      <c r="M29" s="9" t="n"/>
+      <c r="N29" s="9" t="n"/>
+      <c r="O29" s="9" t="n"/>
+      <c r="P29" s="17">
         <f>SUM(D29:O29)</f>
         <v/>
       </c>
@@ -3802,80 +3946,80 @@
           <t>(-) Custo das Mercadorias Vendidas</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="9" t="n">
         <v>-300</v>
       </c>
-      <c r="E30" s="6" t="n"/>
-      <c r="F30" s="6" t="n"/>
-      <c r="G30" s="6" t="n"/>
-      <c r="H30" s="6" t="n"/>
-      <c r="I30" s="6" t="n"/>
-      <c r="J30" s="6" t="n"/>
-      <c r="K30" s="6" t="n"/>
-      <c r="L30" s="6" t="n"/>
-      <c r="M30" s="6" t="n"/>
-      <c r="N30" s="6" t="n"/>
-      <c r="O30" s="6" t="n"/>
-      <c r="P30" s="15">
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="9" t="n"/>
+      <c r="G30" s="9" t="n"/>
+      <c r="H30" s="9" t="n"/>
+      <c r="I30" s="9" t="n"/>
+      <c r="J30" s="9" t="n"/>
+      <c r="K30" s="9" t="n"/>
+      <c r="L30" s="9" t="n"/>
+      <c r="M30" s="9" t="n"/>
+      <c r="N30" s="9" t="n"/>
+      <c r="O30" s="9" t="n"/>
+      <c r="P30" s="17">
         <f>SUM(D30:O30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="17" t="inlineStr">
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">     (=) Lucro Bruto</t>
         </is>
       </c>
-      <c r="D31" s="18">
+      <c r="D31" s="20">
         <f>SUM(D29:D30)</f>
         <v/>
       </c>
-      <c r="E31" s="18">
+      <c r="E31" s="20">
         <f>SUM(E29:E30)</f>
         <v/>
       </c>
-      <c r="F31" s="18">
+      <c r="F31" s="20">
         <f>SUM(F29:F30)</f>
         <v/>
       </c>
-      <c r="G31" s="18">
+      <c r="G31" s="20">
         <f>SUM(G29:G30)</f>
         <v/>
       </c>
-      <c r="H31" s="18">
+      <c r="H31" s="20">
         <f>SUM(H29:H30)</f>
         <v/>
       </c>
-      <c r="I31" s="18">
+      <c r="I31" s="20">
         <f>SUM(I29:I30)</f>
         <v/>
       </c>
-      <c r="J31" s="18">
+      <c r="J31" s="20">
         <f>SUM(J29:J30)</f>
         <v/>
       </c>
-      <c r="K31" s="18">
+      <c r="K31" s="20">
         <f>SUM(K29:K30)</f>
         <v/>
       </c>
-      <c r="L31" s="18">
+      <c r="L31" s="20">
         <f>SUM(L29:L30)</f>
         <v/>
       </c>
-      <c r="M31" s="18">
+      <c r="M31" s="20">
         <f>SUM(M29:M30)</f>
         <v/>
       </c>
-      <c r="N31" s="18">
+      <c r="N31" s="20">
         <f>SUM(N29:N30)</f>
         <v/>
       </c>
-      <c r="O31" s="18">
+      <c r="O31" s="20">
         <f>SUM(O29:O30)</f>
         <v/>
       </c>
-      <c r="P31" s="18">
+      <c r="P31" s="20">
         <f>SUM(P29:P30)</f>
         <v/>
       </c>
@@ -3886,21 +4030,21 @@
           <t>(-) Despesas Operacionais</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n"/>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="6" t="n"/>
-      <c r="G32" s="6" t="n"/>
-      <c r="H32" s="6" t="n"/>
-      <c r="I32" s="6" t="n">
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="9" t="n"/>
+      <c r="G32" s="9" t="n"/>
+      <c r="H32" s="9" t="n"/>
+      <c r="I32" s="9" t="n">
         <v>-90</v>
       </c>
-      <c r="J32" s="6" t="n"/>
-      <c r="K32" s="6" t="n"/>
-      <c r="L32" s="6" t="n"/>
-      <c r="M32" s="6" t="n"/>
-      <c r="N32" s="6" t="n"/>
-      <c r="O32" s="6" t="n"/>
-      <c r="P32" s="15">
+      <c r="J32" s="9" t="n"/>
+      <c r="K32" s="9" t="n"/>
+      <c r="L32" s="9" t="n"/>
+      <c r="M32" s="9" t="n"/>
+      <c r="N32" s="9" t="n"/>
+      <c r="O32" s="9" t="n"/>
+      <c r="P32" s="17">
         <f>SUM(D32:O32)</f>
         <v/>
       </c>
@@ -3911,80 +4055,80 @@
           <t>(-) Depreciação</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n"/>
-      <c r="E33" s="6" t="n"/>
-      <c r="F33" s="6" t="n"/>
-      <c r="G33" s="6" t="n"/>
-      <c r="H33" s="6" t="n"/>
-      <c r="I33" s="6" t="n"/>
-      <c r="J33" s="6" t="n">
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="9" t="n"/>
+      <c r="G33" s="9" t="n"/>
+      <c r="H33" s="9" t="n"/>
+      <c r="I33" s="9" t="n"/>
+      <c r="J33" s="9" t="n">
         <v>-30</v>
       </c>
-      <c r="K33" s="6" t="n"/>
-      <c r="L33" s="6" t="n"/>
-      <c r="M33" s="6" t="n"/>
-      <c r="N33" s="6" t="n"/>
-      <c r="O33" s="6" t="n"/>
-      <c r="P33" s="15">
+      <c r="K33" s="9" t="n"/>
+      <c r="L33" s="9" t="n"/>
+      <c r="M33" s="9" t="n"/>
+      <c r="N33" s="9" t="n"/>
+      <c r="O33" s="9" t="n"/>
+      <c r="P33" s="17">
         <f>SUM(D33:O33)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="17" t="inlineStr">
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">     (=) EBIT</t>
         </is>
       </c>
-      <c r="D34" s="18">
+      <c r="D34" s="20">
         <f>SUM(D31:D33)</f>
         <v/>
       </c>
-      <c r="E34" s="18">
+      <c r="E34" s="20">
         <f>SUM(E31:E33)</f>
         <v/>
       </c>
-      <c r="F34" s="18">
+      <c r="F34" s="20">
         <f>SUM(F31:F33)</f>
         <v/>
       </c>
-      <c r="G34" s="18">
+      <c r="G34" s="20">
         <f>SUM(G31:G33)</f>
         <v/>
       </c>
-      <c r="H34" s="18">
+      <c r="H34" s="20">
         <f>SUM(H31:H33)</f>
         <v/>
       </c>
-      <c r="I34" s="18">
+      <c r="I34" s="20">
         <f>SUM(I31:I33)</f>
         <v/>
       </c>
-      <c r="J34" s="18">
+      <c r="J34" s="20">
         <f>SUM(J31:J33)</f>
         <v/>
       </c>
-      <c r="K34" s="18">
+      <c r="K34" s="20">
         <f>SUM(K31:K33)</f>
         <v/>
       </c>
-      <c r="L34" s="18">
+      <c r="L34" s="20">
         <f>SUM(L31:L33)</f>
         <v/>
       </c>
-      <c r="M34" s="18">
+      <c r="M34" s="20">
         <f>SUM(M31:M33)</f>
         <v/>
       </c>
-      <c r="N34" s="18">
+      <c r="N34" s="20">
         <f>SUM(N31:N33)</f>
         <v/>
       </c>
-      <c r="O34" s="18">
+      <c r="O34" s="20">
         <f>SUM(O31:O33)</f>
         <v/>
       </c>
-      <c r="P34" s="18">
+      <c r="P34" s="20">
         <f>SUM(P31:P33)</f>
         <v/>
       </c>
@@ -3995,80 +4139,80 @@
           <t>(+/-) Resultado Financeiro</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n"/>
-      <c r="E35" s="6" t="n"/>
-      <c r="F35" s="6" t="n"/>
-      <c r="G35" s="6" t="n"/>
-      <c r="H35" s="6" t="n"/>
-      <c r="I35" s="6" t="n"/>
-      <c r="J35" s="6" t="n"/>
-      <c r="K35" s="6" t="n"/>
-      <c r="L35" s="6" t="n">
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="9" t="n"/>
+      <c r="I35" s="9" t="n"/>
+      <c r="J35" s="9" t="n"/>
+      <c r="K35" s="9" t="n"/>
+      <c r="L35" s="9" t="n">
         <v>-10</v>
       </c>
-      <c r="M35" s="6" t="n"/>
-      <c r="N35" s="6" t="n"/>
-      <c r="O35" s="6" t="n"/>
-      <c r="P35" s="15">
+      <c r="M35" s="9" t="n"/>
+      <c r="N35" s="9" t="n"/>
+      <c r="O35" s="9" t="n"/>
+      <c r="P35" s="17">
         <f>SUM(D35:O35)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="17" t="inlineStr">
+      <c r="B36" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">     (=) LAIR</t>
         </is>
       </c>
-      <c r="D36" s="18">
+      <c r="D36" s="20">
         <f>SUM(D34:D35)</f>
         <v/>
       </c>
-      <c r="E36" s="18">
+      <c r="E36" s="20">
         <f>SUM(E34:E35)</f>
         <v/>
       </c>
-      <c r="F36" s="18">
+      <c r="F36" s="20">
         <f>SUM(F34:F35)</f>
         <v/>
       </c>
-      <c r="G36" s="18">
+      <c r="G36" s="20">
         <f>SUM(G34:G35)</f>
         <v/>
       </c>
-      <c r="H36" s="18">
+      <c r="H36" s="20">
         <f>SUM(H34:H35)</f>
         <v/>
       </c>
-      <c r="I36" s="18">
+      <c r="I36" s="20">
         <f>SUM(I34:I35)</f>
         <v/>
       </c>
-      <c r="J36" s="18">
+      <c r="J36" s="20">
         <f>SUM(J34:J35)</f>
         <v/>
       </c>
-      <c r="K36" s="18">
+      <c r="K36" s="20">
         <f>SUM(K34:K35)</f>
         <v/>
       </c>
-      <c r="L36" s="18">
+      <c r="L36" s="20">
         <f>SUM(L34:L35)</f>
         <v/>
       </c>
-      <c r="M36" s="18">
+      <c r="M36" s="20">
         <f>SUM(M34:M35)</f>
         <v/>
       </c>
-      <c r="N36" s="18">
+      <c r="N36" s="20">
         <f>SUM(N34:N35)</f>
         <v/>
       </c>
-      <c r="O36" s="18">
+      <c r="O36" s="20">
         <f>SUM(O34:O35)</f>
         <v/>
       </c>
-      <c r="P36" s="18">
+      <c r="P36" s="20">
         <f>SUM(P34:P35)</f>
         <v/>
       </c>
@@ -4079,86 +4223,86 @@
           <t>(-) IR e CSLL</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n"/>
-      <c r="E37" s="6" t="n"/>
-      <c r="F37" s="6" t="n"/>
-      <c r="G37" s="6" t="n"/>
-      <c r="H37" s="6" t="n"/>
-      <c r="I37" s="6" t="n"/>
-      <c r="J37" s="6" t="n"/>
-      <c r="K37" s="6" t="n"/>
-      <c r="L37" s="6" t="n"/>
-      <c r="M37" s="6" t="n"/>
-      <c r="N37" s="6" t="n">
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="9" t="n"/>
+      <c r="I37" s="9" t="n"/>
+      <c r="J37" s="9" t="n"/>
+      <c r="K37" s="9" t="n"/>
+      <c r="L37" s="9" t="n"/>
+      <c r="M37" s="9" t="n"/>
+      <c r="N37" s="9" t="n">
         <v>-27</v>
       </c>
-      <c r="O37" s="6" t="n"/>
-      <c r="P37" s="15">
+      <c r="O37" s="9" t="n"/>
+      <c r="P37" s="17">
         <f>SUM(D37:O37)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="17" t="inlineStr">
+      <c r="B38" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">     (=) Lucro Líquido</t>
         </is>
       </c>
-      <c r="D38" s="18">
+      <c r="D38" s="20">
         <f>SUM(D36:D37)</f>
         <v/>
       </c>
-      <c r="E38" s="18">
+      <c r="E38" s="20">
         <f>SUM(E36:E37)</f>
         <v/>
       </c>
-      <c r="F38" s="18">
+      <c r="F38" s="20">
         <f>SUM(F36:F37)</f>
         <v/>
       </c>
-      <c r="G38" s="18">
+      <c r="G38" s="20">
         <f>SUM(G36:G37)</f>
         <v/>
       </c>
-      <c r="H38" s="18">
+      <c r="H38" s="20">
         <f>SUM(H36:H37)</f>
         <v/>
       </c>
-      <c r="I38" s="18">
+      <c r="I38" s="20">
         <f>SUM(I36:I37)</f>
         <v/>
       </c>
-      <c r="J38" s="18">
+      <c r="J38" s="20">
         <f>SUM(J36:J37)</f>
         <v/>
       </c>
-      <c r="K38" s="18">
+      <c r="K38" s="20">
         <f>SUM(K36:K37)</f>
         <v/>
       </c>
-      <c r="L38" s="18">
+      <c r="L38" s="20">
         <f>SUM(L36:L37)</f>
         <v/>
       </c>
-      <c r="M38" s="18">
+      <c r="M38" s="20">
         <f>SUM(M36:M37)</f>
         <v/>
       </c>
-      <c r="N38" s="18">
+      <c r="N38" s="20">
         <f>SUM(N36:N37)</f>
         <v/>
       </c>
-      <c r="O38" s="18">
+      <c r="O38" s="20">
         <f>SUM(O36:O37)</f>
         <v/>
       </c>
-      <c r="P38" s="18">
+      <c r="P38" s="20">
         <f>SUM(P36:P37)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B40" s="13" t="inlineStr">
         <is>
           <t>Demonstração dos Fluxos de Caixa</t>
         </is>
@@ -4199,67 +4343,67 @@
       <c r="O40" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="P40" s="11" t="inlineStr">
+      <c r="P40" s="13" t="inlineStr">
         <is>
           <t>Ano 2</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="17" t="inlineStr">
+      <c r="B41" s="19" t="inlineStr">
         <is>
           <t>OPERAÇÕES</t>
         </is>
       </c>
-      <c r="D41" s="18">
+      <c r="D41" s="20">
         <f>SUM(D42:D46)</f>
         <v/>
       </c>
-      <c r="E41" s="18">
+      <c r="E41" s="20">
         <f>SUM(E42:E46)</f>
         <v/>
       </c>
-      <c r="F41" s="18">
+      <c r="F41" s="20">
         <f>SUM(F42:F46)</f>
         <v/>
       </c>
-      <c r="G41" s="18">
+      <c r="G41" s="20">
         <f>SUM(G42:G46)</f>
         <v/>
       </c>
-      <c r="H41" s="18">
+      <c r="H41" s="20">
         <f>SUM(H42:H46)</f>
         <v/>
       </c>
-      <c r="I41" s="18">
+      <c r="I41" s="20">
         <f>SUM(I42:I46)</f>
         <v/>
       </c>
-      <c r="J41" s="18">
+      <c r="J41" s="20">
         <f>SUM(J42:J46)</f>
         <v/>
       </c>
-      <c r="K41" s="18">
+      <c r="K41" s="20">
         <f>SUM(K42:K46)</f>
         <v/>
       </c>
-      <c r="L41" s="18">
+      <c r="L41" s="20">
         <f>SUM(L42:L46)</f>
         <v/>
       </c>
-      <c r="M41" s="18">
+      <c r="M41" s="20">
         <f>SUM(M42:M46)</f>
         <v/>
       </c>
-      <c r="N41" s="18">
+      <c r="N41" s="20">
         <f>SUM(N42:N46)</f>
         <v/>
       </c>
-      <c r="O41" s="18">
+      <c r="O41" s="20">
         <f>SUM(O42:O46)</f>
         <v/>
       </c>
-      <c r="P41" s="18">
+      <c r="P41" s="20">
         <f>SUM(P42:P46)</f>
         <v/>
       </c>
@@ -4270,25 +4414,25 @@
           <t>Recebimentos de Clientes</t>
         </is>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D42" s="9" t="n">
         <v>380</v>
       </c>
-      <c r="E42" s="6" t="n"/>
-      <c r="F42" s="6" t="n">
+      <c r="E42" s="9" t="n"/>
+      <c r="F42" s="9" t="n">
         <v>95</v>
       </c>
-      <c r="G42" s="6" t="n"/>
-      <c r="H42" s="6" t="n">
+      <c r="G42" s="9" t="n"/>
+      <c r="H42" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="I42" s="6" t="n"/>
-      <c r="J42" s="6" t="n"/>
-      <c r="K42" s="6" t="n"/>
-      <c r="L42" s="6" t="n"/>
-      <c r="M42" s="6" t="n"/>
-      <c r="N42" s="6" t="n"/>
-      <c r="O42" s="6" t="n"/>
-      <c r="P42" s="15">
+      <c r="I42" s="9" t="n"/>
+      <c r="J42" s="9" t="n"/>
+      <c r="K42" s="9" t="n"/>
+      <c r="L42" s="9" t="n"/>
+      <c r="M42" s="9" t="n"/>
+      <c r="N42" s="9" t="n"/>
+      <c r="O42" s="9" t="n"/>
+      <c r="P42" s="17">
         <f>SUM(D42:O42)</f>
         <v/>
       </c>
@@ -4299,21 +4443,21 @@
           <t>Pagamentos a Fornecedores</t>
         </is>
       </c>
-      <c r="D43" s="6" t="n"/>
-      <c r="E43" s="6" t="n"/>
-      <c r="F43" s="6" t="n"/>
-      <c r="G43" s="6" t="n">
+      <c r="D43" s="9" t="n"/>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="9" t="n"/>
+      <c r="G43" s="9" t="n">
         <v>-310</v>
       </c>
-      <c r="H43" s="6" t="n"/>
-      <c r="I43" s="6" t="n"/>
-      <c r="J43" s="6" t="n"/>
-      <c r="K43" s="6" t="n"/>
-      <c r="L43" s="6" t="n"/>
-      <c r="M43" s="6" t="n"/>
-      <c r="N43" s="6" t="n"/>
-      <c r="O43" s="6" t="n"/>
-      <c r="P43" s="15">
+      <c r="H43" s="9" t="n"/>
+      <c r="I43" s="9" t="n"/>
+      <c r="J43" s="9" t="n"/>
+      <c r="K43" s="9" t="n"/>
+      <c r="L43" s="9" t="n"/>
+      <c r="M43" s="9" t="n"/>
+      <c r="N43" s="9" t="n"/>
+      <c r="O43" s="9" t="n"/>
+      <c r="P43" s="17">
         <f>SUM(D43:O43)</f>
         <v/>
       </c>
@@ -4324,21 +4468,21 @@
           <t>Pagamentos de Despesas</t>
         </is>
       </c>
-      <c r="D44" s="6" t="n"/>
-      <c r="E44" s="6" t="n"/>
-      <c r="F44" s="6" t="n"/>
-      <c r="G44" s="6" t="n"/>
-      <c r="H44" s="6" t="n"/>
-      <c r="I44" s="6" t="n">
+      <c r="D44" s="9" t="n"/>
+      <c r="E44" s="9" t="n"/>
+      <c r="F44" s="9" t="n"/>
+      <c r="G44" s="9" t="n"/>
+      <c r="H44" s="9" t="n"/>
+      <c r="I44" s="9" t="n">
         <v>-90</v>
       </c>
-      <c r="J44" s="6" t="n"/>
-      <c r="K44" s="6" t="n"/>
-      <c r="L44" s="6" t="n"/>
-      <c r="M44" s="6" t="n"/>
-      <c r="N44" s="6" t="n"/>
-      <c r="O44" s="6" t="n"/>
-      <c r="P44" s="15">
+      <c r="J44" s="9" t="n"/>
+      <c r="K44" s="9" t="n"/>
+      <c r="L44" s="9" t="n"/>
+      <c r="M44" s="9" t="n"/>
+      <c r="N44" s="9" t="n"/>
+      <c r="O44" s="9" t="n"/>
+      <c r="P44" s="17">
         <f>SUM(D44:O44)</f>
         <v/>
       </c>
@@ -4349,21 +4493,21 @@
           <t>Juros Pagos</t>
         </is>
       </c>
-      <c r="D45" s="6" t="n"/>
-      <c r="E45" s="6" t="n"/>
-      <c r="F45" s="6" t="n"/>
-      <c r="G45" s="6" t="n"/>
-      <c r="H45" s="6" t="n"/>
-      <c r="I45" s="6" t="n"/>
-      <c r="J45" s="6" t="n"/>
-      <c r="K45" s="6" t="n"/>
-      <c r="L45" s="6" t="n">
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="9" t="n"/>
+      <c r="G45" s="9" t="n"/>
+      <c r="H45" s="9" t="n"/>
+      <c r="I45" s="9" t="n"/>
+      <c r="J45" s="9" t="n"/>
+      <c r="K45" s="9" t="n"/>
+      <c r="L45" s="9" t="n">
         <v>-10</v>
       </c>
-      <c r="M45" s="6" t="n"/>
-      <c r="N45" s="6" t="n"/>
-      <c r="O45" s="6" t="n"/>
-      <c r="P45" s="15">
+      <c r="M45" s="9" t="n"/>
+      <c r="N45" s="9" t="n"/>
+      <c r="O45" s="9" t="n"/>
+      <c r="P45" s="17">
         <f>SUM(D45:O45)</f>
         <v/>
       </c>
@@ -4374,80 +4518,80 @@
           <t>IR Pago</t>
         </is>
       </c>
-      <c r="D46" s="6" t="n"/>
-      <c r="E46" s="6" t="n"/>
-      <c r="F46" s="6" t="n"/>
-      <c r="G46" s="6" t="n"/>
-      <c r="H46" s="6" t="n"/>
-      <c r="I46" s="6" t="n"/>
-      <c r="J46" s="6" t="n"/>
-      <c r="K46" s="6" t="n"/>
-      <c r="L46" s="6" t="n"/>
-      <c r="M46" s="6" t="n"/>
-      <c r="N46" s="6" t="n">
+      <c r="D46" s="9" t="n"/>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="9" t="n"/>
+      <c r="G46" s="9" t="n"/>
+      <c r="H46" s="9" t="n"/>
+      <c r="I46" s="9" t="n"/>
+      <c r="J46" s="9" t="n"/>
+      <c r="K46" s="9" t="n"/>
+      <c r="L46" s="9" t="n"/>
+      <c r="M46" s="9" t="n"/>
+      <c r="N46" s="9" t="n">
         <v>-20</v>
       </c>
-      <c r="O46" s="6" t="n"/>
-      <c r="P46" s="15">
+      <c r="O46" s="9" t="n"/>
+      <c r="P46" s="17">
         <f>SUM(D46:O46)</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="17" t="inlineStr">
+      <c r="B47" s="19" t="inlineStr">
         <is>
           <t>INVESTIMENTOS</t>
         </is>
       </c>
-      <c r="D47" s="18">
+      <c r="D47" s="20">
         <f>SUM(D48:D48)</f>
         <v/>
       </c>
-      <c r="E47" s="18">
+      <c r="E47" s="20">
         <f>SUM(E48:E48)</f>
         <v/>
       </c>
-      <c r="F47" s="18">
+      <c r="F47" s="20">
         <f>SUM(F48:F48)</f>
         <v/>
       </c>
-      <c r="G47" s="18">
+      <c r="G47" s="20">
         <f>SUM(G48:G48)</f>
         <v/>
       </c>
-      <c r="H47" s="18">
+      <c r="H47" s="20">
         <f>SUM(H48:H48)</f>
         <v/>
       </c>
-      <c r="I47" s="18">
+      <c r="I47" s="20">
         <f>SUM(I48:I48)</f>
         <v/>
       </c>
-      <c r="J47" s="18">
+      <c r="J47" s="20">
         <f>SUM(J48:J48)</f>
         <v/>
       </c>
-      <c r="K47" s="18">
+      <c r="K47" s="20">
         <f>SUM(K48:K48)</f>
         <v/>
       </c>
-      <c r="L47" s="18">
+      <c r="L47" s="20">
         <f>SUM(L48:L48)</f>
         <v/>
       </c>
-      <c r="M47" s="18">
+      <c r="M47" s="20">
         <f>SUM(M48:M48)</f>
         <v/>
       </c>
-      <c r="N47" s="18">
+      <c r="N47" s="20">
         <f>SUM(N48:N48)</f>
         <v/>
       </c>
-      <c r="O47" s="18">
+      <c r="O47" s="20">
         <f>SUM(O48:O48)</f>
         <v/>
       </c>
-      <c r="P47" s="18">
+      <c r="P47" s="20">
         <f>SUM(P48:P48)</f>
         <v/>
       </c>
@@ -4458,80 +4602,80 @@
           <t>Aquisição de Imobilizado</t>
         </is>
       </c>
-      <c r="D48" s="6" t="n"/>
-      <c r="E48" s="6" t="n"/>
-      <c r="F48" s="6" t="n"/>
-      <c r="G48" s="6" t="n"/>
-      <c r="H48" s="6" t="n"/>
-      <c r="I48" s="6" t="n"/>
-      <c r="J48" s="6" t="n"/>
-      <c r="K48" s="6" t="n"/>
-      <c r="L48" s="6" t="n"/>
-      <c r="M48" s="6" t="n">
+      <c r="D48" s="9" t="n"/>
+      <c r="E48" s="9" t="n"/>
+      <c r="F48" s="9" t="n"/>
+      <c r="G48" s="9" t="n"/>
+      <c r="H48" s="9" t="n"/>
+      <c r="I48" s="9" t="n"/>
+      <c r="J48" s="9" t="n"/>
+      <c r="K48" s="9" t="n"/>
+      <c r="L48" s="9" t="n"/>
+      <c r="M48" s="9" t="n">
         <v>-45</v>
       </c>
-      <c r="N48" s="6" t="n"/>
-      <c r="O48" s="6" t="n"/>
-      <c r="P48" s="15">
+      <c r="N48" s="9" t="n"/>
+      <c r="O48" s="9" t="n"/>
+      <c r="P48" s="17">
         <f>SUM(D48:O48)</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="17" t="inlineStr">
+      <c r="B49" s="19" t="inlineStr">
         <is>
           <t>FINANCIAMENTOS</t>
         </is>
       </c>
-      <c r="D49" s="18">
+      <c r="D49" s="20">
         <f>SUM(D50:D52)</f>
         <v/>
       </c>
-      <c r="E49" s="18">
+      <c r="E49" s="20">
         <f>SUM(E50:E52)</f>
         <v/>
       </c>
-      <c r="F49" s="18">
+      <c r="F49" s="20">
         <f>SUM(F50:F52)</f>
         <v/>
       </c>
-      <c r="G49" s="18">
+      <c r="G49" s="20">
         <f>SUM(G50:G52)</f>
         <v/>
       </c>
-      <c r="H49" s="18">
+      <c r="H49" s="20">
         <f>SUM(H50:H52)</f>
         <v/>
       </c>
-      <c r="I49" s="18">
+      <c r="I49" s="20">
         <f>SUM(I50:I52)</f>
         <v/>
       </c>
-      <c r="J49" s="18">
+      <c r="J49" s="20">
         <f>SUM(J50:J52)</f>
         <v/>
       </c>
-      <c r="K49" s="18">
+      <c r="K49" s="20">
         <f>SUM(K50:K52)</f>
         <v/>
       </c>
-      <c r="L49" s="18">
+      <c r="L49" s="20">
         <f>SUM(L50:L52)</f>
         <v/>
       </c>
-      <c r="M49" s="18">
+      <c r="M49" s="20">
         <f>SUM(M50:M52)</f>
         <v/>
       </c>
-      <c r="N49" s="18">
+      <c r="N49" s="20">
         <f>SUM(N50:N52)</f>
         <v/>
       </c>
-      <c r="O49" s="18">
+      <c r="O49" s="20">
         <f>SUM(O50:O52)</f>
         <v/>
       </c>
-      <c r="P49" s="18">
+      <c r="P49" s="20">
         <f>SUM(P50:P52)</f>
         <v/>
       </c>
@@ -4542,21 +4686,21 @@
           <t>Captação de Empréstimos</t>
         </is>
       </c>
-      <c r="D50" s="6" t="n"/>
-      <c r="E50" s="6" t="n"/>
-      <c r="F50" s="6" t="n"/>
-      <c r="G50" s="6" t="n"/>
-      <c r="H50" s="6" t="n"/>
-      <c r="I50" s="6" t="n"/>
-      <c r="J50" s="6" t="n"/>
-      <c r="K50" s="6" t="n">
+      <c r="D50" s="9" t="n"/>
+      <c r="E50" s="9" t="n"/>
+      <c r="F50" s="9" t="n"/>
+      <c r="G50" s="9" t="n"/>
+      <c r="H50" s="9" t="n"/>
+      <c r="I50" s="9" t="n"/>
+      <c r="J50" s="9" t="n"/>
+      <c r="K50" s="9" t="n">
         <v>80</v>
       </c>
-      <c r="L50" s="6" t="n"/>
-      <c r="M50" s="6" t="n"/>
-      <c r="N50" s="6" t="n"/>
-      <c r="O50" s="6" t="n"/>
-      <c r="P50" s="15">
+      <c r="L50" s="9" t="n"/>
+      <c r="M50" s="9" t="n"/>
+      <c r="N50" s="9" t="n"/>
+      <c r="O50" s="9" t="n"/>
+      <c r="P50" s="17">
         <f>SUM(D50:O50)</f>
         <v/>
       </c>
@@ -4567,21 +4711,21 @@
           <t>Amortização de Empréstimos</t>
         </is>
       </c>
-      <c r="D51" s="6" t="n"/>
-      <c r="E51" s="6" t="n"/>
-      <c r="F51" s="6" t="n"/>
-      <c r="G51" s="6" t="n"/>
-      <c r="H51" s="6" t="n"/>
-      <c r="I51" s="6" t="n"/>
-      <c r="J51" s="6" t="n"/>
-      <c r="K51" s="6" t="n"/>
-      <c r="L51" s="6" t="n">
+      <c r="D51" s="9" t="n"/>
+      <c r="E51" s="9" t="n"/>
+      <c r="F51" s="9" t="n"/>
+      <c r="G51" s="9" t="n"/>
+      <c r="H51" s="9" t="n"/>
+      <c r="I51" s="9" t="n"/>
+      <c r="J51" s="9" t="n"/>
+      <c r="K51" s="9" t="n"/>
+      <c r="L51" s="9" t="n">
         <v>-50</v>
       </c>
-      <c r="M51" s="6" t="n"/>
-      <c r="N51" s="6" t="n"/>
-      <c r="O51" s="6" t="n"/>
-      <c r="P51" s="15">
+      <c r="M51" s="9" t="n"/>
+      <c r="N51" s="9" t="n"/>
+      <c r="O51" s="9" t="n"/>
+      <c r="P51" s="17">
         <f>SUM(D51:O51)</f>
         <v/>
       </c>
@@ -4592,80 +4736,80 @@
           <t>Dividendos Pagos</t>
         </is>
       </c>
-      <c r="D52" s="6" t="n"/>
-      <c r="E52" s="6" t="n"/>
-      <c r="F52" s="6" t="n"/>
-      <c r="G52" s="6" t="n"/>
-      <c r="H52" s="6" t="n"/>
-      <c r="I52" s="6" t="n"/>
-      <c r="J52" s="6" t="n"/>
-      <c r="K52" s="6" t="n"/>
-      <c r="L52" s="6" t="n"/>
-      <c r="M52" s="6" t="n"/>
-      <c r="N52" s="6" t="n"/>
-      <c r="O52" s="6" t="n">
+      <c r="D52" s="9" t="n"/>
+      <c r="E52" s="9" t="n"/>
+      <c r="F52" s="9" t="n"/>
+      <c r="G52" s="9" t="n"/>
+      <c r="H52" s="9" t="n"/>
+      <c r="I52" s="9" t="n"/>
+      <c r="J52" s="9" t="n"/>
+      <c r="K52" s="9" t="n"/>
+      <c r="L52" s="9" t="n"/>
+      <c r="M52" s="9" t="n"/>
+      <c r="N52" s="9" t="n"/>
+      <c r="O52" s="9" t="n">
         <v>-25</v>
       </c>
-      <c r="P52" s="15">
+      <c r="P52" s="17">
         <f>SUM(D52:O52)</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="17" t="inlineStr">
+      <c r="B53" s="19" t="inlineStr">
         <is>
           <t>VARIAÇÃO NO CAIXA</t>
         </is>
       </c>
-      <c r="D53" s="18">
+      <c r="D53" s="20">
         <f>D41+D47+D49</f>
         <v/>
       </c>
-      <c r="E53" s="18">
+      <c r="E53" s="20">
         <f>E41+E47+E49</f>
         <v/>
       </c>
-      <c r="F53" s="18">
+      <c r="F53" s="20">
         <f>F41+F47+F49</f>
         <v/>
       </c>
-      <c r="G53" s="18">
+      <c r="G53" s="20">
         <f>G41+G47+G49</f>
         <v/>
       </c>
-      <c r="H53" s="18">
+      <c r="H53" s="20">
         <f>H41+H47+H49</f>
         <v/>
       </c>
-      <c r="I53" s="18">
+      <c r="I53" s="20">
         <f>I41+I47+I49</f>
         <v/>
       </c>
-      <c r="J53" s="18">
+      <c r="J53" s="20">
         <f>J41+J47+J49</f>
         <v/>
       </c>
-      <c r="K53" s="18">
+      <c r="K53" s="20">
         <f>K41+K47+K49</f>
         <v/>
       </c>
-      <c r="L53" s="18">
+      <c r="L53" s="20">
         <f>L41+L47+L49</f>
         <v/>
       </c>
-      <c r="M53" s="18">
+      <c r="M53" s="20">
         <f>M41+M47+M49</f>
         <v/>
       </c>
-      <c r="N53" s="18">
+      <c r="N53" s="20">
         <f>N41+N47+N49</f>
         <v/>
       </c>
-      <c r="O53" s="18">
+      <c r="O53" s="20">
         <f>O41+O47+O49</f>
         <v/>
       </c>
-      <c r="P53" s="18">
+      <c r="P53" s="20">
         <f>P41+P47+P49</f>
         <v/>
       </c>
@@ -4676,34 +4820,34 @@
           <t xml:space="preserve">    Saldo inicial de caixa</t>
         </is>
       </c>
-      <c r="P54" s="14" t="n">
+      <c r="P54" s="16" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="17" t="inlineStr">
+      <c r="B55" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    Saldo final de caixa</t>
         </is>
       </c>
-      <c r="P55" s="15">
+      <c r="P55" s="17">
         <f>P54+P53</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="19" t="inlineStr">
+      <c r="B57" s="21" t="inlineStr">
         <is>
           <t>Caixa final da DFC menos Caixa do BP (tem que dar zero)</t>
         </is>
       </c>
-      <c r="P57" s="15">
+      <c r="P57" s="17">
         <f>P55-P6</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="11" t="inlineStr">
+      <c r="B59" s="13" t="inlineStr">
         <is>
           <t>Indicadores (automáticos)</t>
         </is>
@@ -4715,7 +4859,7 @@
           <t>Margem bruta</t>
         </is>
       </c>
-      <c r="P60" s="21">
+      <c r="P60" s="23">
         <f>IF(P29=0,"",P31/P29)</f>
         <v/>
       </c>
@@ -4726,7 +4870,7 @@
           <t>Margem líquida</t>
         </is>
       </c>
-      <c r="P61" s="21">
+      <c r="P61" s="23">
         <f>IF(P29=0,"",P38/P29)</f>
         <v/>
       </c>
@@ -4737,7 +4881,7 @@
           <t>% financiado por capital próprio (PL / Ativo)</t>
         </is>
       </c>
-      <c r="P62" s="21">
+      <c r="P62" s="23">
         <f>IF(P12=0,"",SUM(P22:P23)/P12)</f>
         <v/>
       </c>
@@ -4748,7 +4892,7 @@
           <t>ROE (LL / PL final)</t>
         </is>
       </c>
-      <c r="P63" s="21">
+      <c r="P63" s="23">
         <f>IF(SUM(P22:P23)=0,"",P38/SUM(P22:P23))</f>
         <v/>
       </c>
@@ -4764,17 +4908,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="3" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4787,14 +4934,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Uma linha por movimento. Se a transação mexe em duas contas do mesmo lado (ex: sai caixa, entra estoque), usa as duas linhas.</t>
+          <t>Uma linha por movimento: escreve a conta e o valor, com sinal. Transação que mexe em três contas do mesmo lado usa as três linhas. A coluna Check acusa se aquela transação fechou.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Transação</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -4807,631 +4954,888 @@
           <t>ATIVO</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>PASSIVO</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>PATRIMÔNIO LÍQUIDO</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="4" t="n">
+    <row r="5">
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>conta</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>conta</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>conta</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Vendas do ano de 520, sendo 380 à vista e 140 a prazo; o custo das mercadorias vendidas foi de 300</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Caixa</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n">
         <v>380</v>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Lucros Acumulados</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="n">
         <v>220</v>
       </c>
-      <c r="H5" s="8">
-        <f>IF(COUNT(C5:C6,E5:E6,G5:G6)=0,"",IF(SUM(C5:C6)-SUM(E5:E6)-SUM(G5:G6)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="C6" s="6" t="n">
+      <c r="K6" s="6">
+        <f>IF(COUNT(D6:D8,G6:G8,J6:J8)=0,"",IF(SUM(D6:D8)-SUM(G6:G8)-SUM(J6:J8)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Contas a Receber</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
         <v>140</v>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="9" t="n"/>
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="4" t="n">
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="9" t="n"/>
+    </row>
+    <row r="8">
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Estoques</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>-300</v>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="9" t="n"/>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="9" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Compras de estoque no ano: 330, integralmente a prazo</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Estoques</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
         <v>330</v>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Fornecedores</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="n">
         <v>330</v>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="8">
-        <f>IF(COUNT(C7:C8,E7:E8,G7:G8)=0,"",IF(SUM(C7:C8)-SUM(E7:E8)-SUM(G7:G8)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="I9" s="8" t="n"/>
+      <c r="J9" s="9" t="n"/>
+      <c r="K9" s="6">
+        <f>IF(COUNT(D9:D10,G9:G10,J9:J10)=0,"",IF(SUM(D9:D10)-SUM(G9:G10)-SUM(J9:J10)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="4" t="n">
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="9" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Recebimento de 95 de clientes, referente a vendas de anos anteriores</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Caixa</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
         <v>95</v>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="8">
-        <f>IF(COUNT(C9:C10,E9:E10,G9:G10)=0,"",IF(SUM(C9:C10)-SUM(E9:E10)-SUM(G9:G10)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="C10" s="6" t="n">
+      <c r="I11" s="8" t="n"/>
+      <c r="J11" s="9" t="n"/>
+      <c r="K11" s="6">
+        <f>IF(COUNT(D11:D12,G11:G12,J11:J12)=0,"",IF(SUM(D11:D12)-SUM(G11:G12)-SUM(J11:J12)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Contas a Receber</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
         <v>-95</v>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="9" t="n"/>
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G10" s="6" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="4" t="n">
+      <c r="I12" s="8" t="n"/>
+      <c r="J12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Pagamento de 310 a fornecedores</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Caixa</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n">
         <v>-310</v>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>Fornecedores</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="n">
         <v>-310</v>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="8">
-        <f>IF(COUNT(C11:C12,E11:E12,G11:G12)=0,"",IF(SUM(C11:C12)-SUM(E11:E12)-SUM(G11:G12)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="9" t="n"/>
+      <c r="K13" s="6">
+        <f>IF(COUNT(D13:D14,G13:G14,J13:J14)=0,"",IF(SUM(D13:D14)-SUM(G13:G14)-SUM(J13:J14)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="9" t="n"/>
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="4" t="n">
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Cliente corporativo adianta 25 por uma encomenda que só será entregue no ano seguinte</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Caixa</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>Adiantamentos de Clientes</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="8">
-        <f>IF(COUNT(C13:C14,E13:E14,G13:G14)=0,"",IF(SUM(C13:C14)-SUM(E13:E14)-SUM(G13:G14)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="I15" s="8" t="n"/>
+      <c r="J15" s="9" t="n"/>
+      <c r="K15" s="6">
+        <f>IF(COUNT(D15:D16,G15:G16,J15:J16)=0,"",IF(SUM(D15:D16)-SUM(G15:G16)-SUM(J15:J16)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G14" s="6" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="4" t="n">
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Despesas de vendas e administrativas de 90, pagas à vista</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Caixa</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n">
         <v>-90</v>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>Lucros Acumulados</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="n">
         <v>-90</v>
       </c>
-      <c r="H15" s="8">
-        <f>IF(COUNT(C15:C16,E15:E16,G15:G16)=0,"",IF(SUM(C15:C16)-SUM(E15:E16)-SUM(G15:G16)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="K17" s="6">
+        <f>IF(COUNT(D17:D18,G17:G18,J17:J18)=0,"",IF(SUM(D17:D18)-SUM(G17:G18)-SUM(J17:J18)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="9" t="n"/>
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G16" s="6" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="4" t="n">
+      <c r="I18" s="8" t="n"/>
+      <c r="J18" s="9" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Depreciação do imobilizado no ano: 30</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n">
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>(-) Depreciação Acumulada</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n">
         <v>-30</v>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="9" t="n"/>
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>Lucros Acumulados</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="n">
         <v>-30</v>
       </c>
-      <c r="H17" s="8">
-        <f>IF(COUNT(C17:C18,E17:E18,G17:G18)=0,"",IF(SUM(C17:C18)-SUM(E17:E18)-SUM(G17:G18)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="K19" s="6">
+        <f>IF(COUNT(D19:D20,G19:G20,J19:J20)=0,"",IF(SUM(D19:D20)-SUM(G19:G20)-SUM(J19:J20)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="9" t="n"/>
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G18" s="6" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="4" t="n">
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Captação de novo empréstimo bancário de 80</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n">
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Caixa</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n">
         <v>80</v>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Empréstimos</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="n">
         <v>80</v>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="8">
-        <f>IF(COUNT(C19:C20,E19:E20,G19:G20)=0,"",IF(SUM(C19:C20)-SUM(E19:E20)-SUM(G19:G20)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="I21" s="8" t="n"/>
+      <c r="J21" s="9" t="n"/>
+      <c r="K21" s="6">
+        <f>IF(COUNT(D21:D22,G21:G22,J21:J22)=0,"",IF(SUM(D21:D22)-SUM(G21:G22)-SUM(J21:J22)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="9" t="n"/>
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G20" s="6" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="4" t="n">
+      <c r="I22" s="8" t="n"/>
+      <c r="J22" s="9" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Amortização de 50 do principal da dívida e pagamento de 10 de juros do período</t>
         </is>
       </c>
-      <c r="C21" s="6" t="n">
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Caixa</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="n">
         <v>-60</v>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="E23" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>Empréstimos</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="n">
         <v>-50</v>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>Lucros Acumulados</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="n">
         <v>-10</v>
       </c>
-      <c r="H21" s="8">
-        <f>IF(COUNT(C21:C22,E21:E22,G21:G22)=0,"",IF(SUM(C21:C22)-SUM(E21:E22)-SUM(G21:G22)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="K23" s="6">
+        <f>IF(COUNT(D23:D24,G23:G24,J23:J24)=0,"",IF(SUM(D23:D24)-SUM(G23:G24)-SUM(J23:J24)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="9" t="n"/>
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G22" s="6" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="4" t="n">
+      <c r="I24" s="8" t="n"/>
+      <c r="J24" s="9" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>Compra de um novo forno por 120, pagando 45 à vista e 75 em financiamento de longo prazo</t>
         </is>
       </c>
-      <c r="C23" s="6" t="n">
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Caixa</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n">
         <v>-45</v>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="E25" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Financiamento a Pagar (LP)</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="n">
         <v>75</v>
       </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="8">
-        <f>IF(COUNT(C23:C24,E23:E24,G23:G24)=0,"",IF(SUM(C23:C24)-SUM(E23:E24)-SUM(G23:G24)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="C24" s="6" t="n">
+      <c r="I25" s="8" t="n"/>
+      <c r="J25" s="9" t="n"/>
+      <c r="K25" s="6">
+        <f>IF(COUNT(D25:D26,G25:G26,J25:J26)=0,"",IF(SUM(D25:D26)-SUM(G25:G26)-SUM(J25:J26)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Imobilizado</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n">
         <v>120</v>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="E26" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="9" t="n"/>
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G24" s="6" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="4" t="n">
+      <c r="I26" s="8" t="n"/>
+      <c r="J26" s="9" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>IR e CSLL do ano: 27, sendo 20 pagos à vista e 7 a recolher no ano seguinte</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n">
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Caixa</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="n">
         <v>-20</v>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="E27" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>IR a Pagar</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>Lucros Acumulados</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="n">
         <v>-27</v>
       </c>
-      <c r="H25" s="8">
-        <f>IF(COUNT(C25:C26,E25:E26,G25:G26)=0,"",IF(SUM(C25:C26)-SUM(E25:E26)-SUM(G25:G26)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="K27" s="6">
+        <f>IF(COUNT(D27:D28,G27:G28,J27:J28)=0,"",IF(SUM(D27:D28)-SUM(G27:G28)-SUM(J27:J28)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="9" t="n"/>
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G26" s="6" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="4" t="n">
+      <c r="I28" s="8" t="n"/>
+      <c r="J28" s="9" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>Dividendos de 25 declarados e pagos em dinheiro</t>
         </is>
       </c>
-      <c r="C27" s="6" t="n">
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Caixa</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n">
         <v>-25</v>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="E29" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F29" s="8" t="n"/>
+      <c r="G29" s="9" t="n"/>
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="I29" s="8" t="inlineStr">
+        <is>
+          <t>Lucros Acumulados</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="n">
         <v>-25</v>
       </c>
-      <c r="H27" s="8">
-        <f>IF(COUNT(C27:C28,E27:E28,G27:G28)=0,"",IF(SUM(C27:C28)-SUM(E27:E28)-SUM(G27:G28)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="K29" s="6">
+        <f>IF(COUNT(D29:D30,G29:G30,J29:J30)=0,"",IF(SUM(D29:D30)-SUM(G29:G30)-SUM(J29:J30)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E28" s="6" t="n"/>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F30" s="8" t="n"/>
+      <c r="G30" s="9" t="n"/>
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G28" s="6" t="n"/>
+      <c r="I30" s="8" t="n"/>
+      <c r="J30" s="9" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="39">
+    <mergeCell ref="F4:G4"/>
     <mergeCell ref="B27:B28"/>
-    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="K21:K22"/>
     <mergeCell ref="B17:B18"/>
-    <mergeCell ref="A7:A8"/>
     <mergeCell ref="B11:B12"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C4:D4"/>
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="A27:A28"/>
-    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="K27:K28"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="A25:A26"/>
-    <mergeCell ref="H7:H8"/>
     <mergeCell ref="B19:B20"/>
-    <mergeCell ref="H19:H20"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A5:A6"/>
     <mergeCell ref="B9:B10"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="H27:H28"/>
     <mergeCell ref="A17:A18"/>
+    <mergeCell ref="K17:K18"/>
     <mergeCell ref="A13:A14"/>
+    <mergeCell ref="K23:K24"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="K13:K14"/>
     <mergeCell ref="A23:A24"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="A6:A8"/>
     <mergeCell ref="A19:A20"/>
-    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="K19:K20"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K9:K10"/>
     <mergeCell ref="A9:A10"/>
+    <mergeCell ref="K25:K26"/>
     <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B7:B8"/>
     <mergeCell ref="B25:B26"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="K29:K30"/>
     <mergeCell ref="B21:B22"/>
     <mergeCell ref="A11:A12"/>
   </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Caixa,Contas a Receber,Estoques,Imobilizado,(-) Depreciação Acumulada"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Fornecedores,Adiantamentos de Clientes,IR a Pagar,Empréstimos,Financiamento a Pagar (LP)"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Capital Social,Lucros Acumulados"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ContabilidadeFinanceira/Treinos/Ex5_MarGrosso.xlsx
+++ b/ContabilidadeFinanceira/Treinos/Ex5_MarGrosso.xlsx
@@ -1226,7 +1226,7 @@
       <c r="J30" s="9" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="40">
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="B27:B28"/>
     <mergeCell ref="K21:K22"/>
@@ -1244,6 +1244,7 @@
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="K17:K18"/>
@@ -1314,7 +1315,7 @@
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Cervejaria Mar Grosso S.A.  |  Ano 2  |  valores em R$ mil</t>
+          <t>Cervejaria Mar Grosso S.A.</t>
         </is>
       </c>
       <c r="D1" s="11" t="inlineStr">
@@ -1324,6 +1325,11 @@
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Ano 2  |  valores em R$ mil</t>
+        </is>
+      </c>
       <c r="D2" s="12" t="inlineStr">
         <is>
           <t>Vendas do ano de 520, sendo 380 à vista e 140 a prazo; o cus</t>
@@ -3100,6 +3106,9 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3136,7 +3145,7 @@
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Cervejaria Mar Grosso S.A.  |  Ano 2  |  valores em R$ mil</t>
+          <t>Cervejaria Mar Grosso S.A.</t>
         </is>
       </c>
       <c r="D1" s="11" t="inlineStr">
@@ -3146,6 +3155,11 @@
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Ano 2  |  valores em R$ mil</t>
+        </is>
+      </c>
       <c r="D2" s="12" t="inlineStr">
         <is>
           <t>Vendas do ano de 520, sendo 380 à vista e 140 a prazo; o cus</t>
@@ -4898,6 +4912,9 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5784,7 +5801,7 @@
       <c r="J30" s="9" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="40">
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="B27:B28"/>
     <mergeCell ref="K21:K22"/>
@@ -5802,6 +5819,7 @@
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="K17:K18"/>
